--- a/Chile_viral.xlsx
+++ b/Chile_viral.xlsx
@@ -121,21 +121,21 @@
     <t>text</t>
   </si>
   <si>
+    <t>E_D</t>
+  </si>
+  <si>
+    <t>Endorsement</t>
+  </si>
+  <si>
+    <t>Denuncia</t>
+  </si>
+  <si>
     <t>Eval</t>
   </si>
   <si>
     <t>Personal</t>
   </si>
   <si>
-    <t>E_D</t>
-  </si>
-  <si>
-    <t>Endorsement</t>
-  </si>
-  <si>
-    <t>Denuncia</t>
-  </si>
-  <si>
     <t>Pol_pub</t>
   </si>
   <si>
@@ -172,7 +172,7 @@
     <t>Tipo de actor</t>
   </si>
   <si>
-    <t>Posicionamiento de actor</t>
+    <t>General position</t>
   </si>
   <si>
     <t>NA</t>
@@ -2305,7 +2305,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -2330,6 +2330,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2345,7 +2351,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2366,6 +2372,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
@@ -2599,7 +2608,6 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col hidden="1" min="5" max="26" width="12.63"/>
     <col hidden="1" min="28" max="28" width="12.63"/>
     <col hidden="1" min="31" max="33" width="12.63"/>
     <col hidden="1" min="35" max="36" width="12.63"/>
@@ -2766,7 +2774,7 @@
       <c r="BB1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BC1" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2780,7 +2788,7 @@
       <c r="C2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>45994.90087962963</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2810,7 +2818,7 @@
       <c r="M2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="8">
         <v>46056.273368055554</v>
       </c>
       <c r="O2" s="1" t="s">
@@ -2861,7 +2869,7 @@
       <c r="AD2" s="1">
         <v>206258.0</v>
       </c>
-      <c r="AE2" s="8">
+      <c r="AE2" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF2" s="1">
@@ -2882,24 +2890,24 @@
       <c r="AK2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AL2" s="10"/>
+      <c r="AM2" s="10"/>
+      <c r="AN2" s="10"/>
+      <c r="AO2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9" t="s">
+      <c r="AP2" s="10"/>
+      <c r="AQ2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9" t="s">
+      <c r="AR2" s="10"/>
+      <c r="AS2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AT2" s="9">
+      <c r="AT2" s="10">
         <v>2.0</v>
       </c>
-      <c r="AU2" s="10">
+      <c r="AU2" s="11">
         <v>1.0</v>
       </c>
       <c r="AV2" s="6" t="s">
@@ -2935,7 +2943,7 @@
       <c r="C3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>45994.769467592596</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2965,7 +2973,7 @@
       <c r="M3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="8">
         <v>46007.259409722225</v>
       </c>
       <c r="O3" s="1" t="s">
@@ -3016,7 +3024,7 @@
       <c r="AD3" s="1">
         <v>77009.0</v>
       </c>
-      <c r="AE3" s="8">
+      <c r="AE3" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF3" s="1">
@@ -3037,12 +3045,12 @@
       <c r="AK3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AL3" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
-      <c r="AO3" s="1"/>
+      <c r="AO3" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1" t="s">
         <v>81</v>
@@ -3092,7 +3100,7 @@
       <c r="C4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <v>45994.52866898148</v>
       </c>
       <c r="E4" s="1">
@@ -3122,7 +3130,7 @@
       <c r="M4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="8">
         <v>45994.534583333334</v>
       </c>
       <c r="O4" s="1" t="s">
@@ -3173,7 +3181,7 @@
       <c r="AD4" s="1">
         <v>69810.0</v>
       </c>
-      <c r="AE4" s="8">
+      <c r="AE4" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF4" s="1">
@@ -3194,17 +3202,17 @@
       <c r="AK4" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AL4" s="4" t="s">
-        <v>41</v>
+      <c r="AL4" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="AO4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP4" s="1"/>
       <c r="AQ4" s="1" t="s">
         <v>96</v>
       </c>
@@ -3248,7 +3256,7 @@
       <c r="C5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <v>45995.94550925926</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -3278,7 +3286,7 @@
       <c r="M5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="8">
         <v>46007.256944444445</v>
       </c>
       <c r="O5" s="1" t="s">
@@ -3329,7 +3337,7 @@
       <c r="AD5" s="1">
         <v>1003996.0</v>
       </c>
-      <c r="AE5" s="8">
+      <c r="AE5" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF5" s="1">
@@ -3350,22 +3358,22 @@
       <c r="AK5" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AL5" s="10"/>
-      <c r="AM5" s="10"/>
-      <c r="AN5" s="1" t="s">
+      <c r="AL5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AO5" s="10"/>
-      <c r="AP5" s="9" t="s">
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ5" s="10"/>
-      <c r="AR5" s="10"/>
-      <c r="AS5" s="10"/>
-      <c r="AT5" s="10">
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU5" s="10">
+      <c r="AU5" s="11">
         <v>2.0</v>
       </c>
       <c r="AV5" s="6" t="s">
@@ -3404,7 +3412,7 @@
       <c r="C6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <v>45994.94326388889</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -3434,7 +3442,7 @@
       <c r="M6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="8">
         <v>45994.944918981484</v>
       </c>
       <c r="O6" s="1" t="s">
@@ -3485,7 +3493,7 @@
       <c r="AD6" s="1">
         <v>149402.0</v>
       </c>
-      <c r="AE6" s="8">
+      <c r="AE6" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF6" s="1">
@@ -3506,26 +3514,26 @@
       <c r="AK6" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="AL6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM6" s="9" t="s">
+      <c r="AL6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AN6" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO6" s="10"/>
-      <c r="AP6" s="9" t="s">
+      <c r="AO6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP6" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ6" s="10"/>
-      <c r="AR6" s="10"/>
-      <c r="AS6" s="10"/>
-      <c r="AT6" s="10">
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU6" s="10">
+      <c r="AU6" s="11">
         <v>1.0</v>
       </c>
       <c r="AV6" s="6" t="s">
@@ -3561,7 +3569,7 @@
       <c r="C7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <v>45994.59710648148</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -3591,7 +3599,7 @@
       <c r="M7" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="8">
         <v>46007.24946759259</v>
       </c>
       <c r="O7" s="1" t="s">
@@ -3642,7 +3650,7 @@
       <c r="AD7" s="1">
         <v>240874.0</v>
       </c>
-      <c r="AE7" s="8">
+      <c r="AE7" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF7" s="1">
@@ -3663,22 +3671,22 @@
       <c r="AK7" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AL7" s="10"/>
-      <c r="AM7" s="10"/>
-      <c r="AN7" s="1" t="s">
+      <c r="AL7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AO7" s="10"/>
-      <c r="AP7" s="9" t="s">
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ7" s="10"/>
-      <c r="AR7" s="10"/>
-      <c r="AS7" s="10"/>
-      <c r="AT7" s="9">
+      <c r="AO7" s="11"/>
+      <c r="AP7" s="11"/>
+      <c r="AQ7" s="11"/>
+      <c r="AR7" s="11"/>
+      <c r="AS7" s="11"/>
+      <c r="AT7" s="10">
         <v>3.0</v>
       </c>
-      <c r="AU7" s="10">
+      <c r="AU7" s="11">
         <v>1.0</v>
       </c>
       <c r="AV7" s="6" t="s">
@@ -3714,7 +3722,7 @@
       <c r="C8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <v>45995.5050462963</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -3744,7 +3752,7 @@
       <c r="M8" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="8">
         <v>46020.82047453704</v>
       </c>
       <c r="O8" s="1" t="s">
@@ -3795,7 +3803,7 @@
       <c r="AD8" s="1">
         <v>158377.0</v>
       </c>
-      <c r="AE8" s="8">
+      <c r="AE8" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF8" s="1">
@@ -3816,22 +3824,22 @@
       <c r="AK8" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="AL8" s="10"/>
-      <c r="AM8" s="10"/>
-      <c r="AN8" s="1" t="s">
+      <c r="AL8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AO8" s="10"/>
-      <c r="AP8" s="9" t="s">
+      <c r="AM8" s="11"/>
+      <c r="AN8" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ8" s="10"/>
-      <c r="AR8" s="10"/>
-      <c r="AS8" s="10"/>
-      <c r="AT8" s="10">
+      <c r="AO8" s="11"/>
+      <c r="AP8" s="11"/>
+      <c r="AQ8" s="11"/>
+      <c r="AR8" s="11"/>
+      <c r="AS8" s="11"/>
+      <c r="AT8" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU8" s="10">
+      <c r="AU8" s="11">
         <v>1.0</v>
       </c>
       <c r="AV8" s="6" t="s">
@@ -3867,7 +3875,7 @@
       <c r="C9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <v>45994.71802083333</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -3897,7 +3905,7 @@
       <c r="M9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="8">
         <v>46010.6821412037</v>
       </c>
       <c r="O9" s="1" t="s">
@@ -3948,7 +3956,7 @@
       <c r="AD9" s="1">
         <v>125191.0</v>
       </c>
-      <c r="AE9" s="8">
+      <c r="AE9" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF9" s="1">
@@ -3969,22 +3977,22 @@
       <c r="AK9" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="AL9" s="9"/>
-      <c r="AM9" s="9"/>
-      <c r="AN9" s="1" t="s">
+      <c r="AL9" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="10" t="s">
+        <v>110</v>
+      </c>
       <c r="AO9" s="10"/>
-      <c r="AP9" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ9" s="10"/>
-      <c r="AR9" s="10"/>
-      <c r="AS9" s="10"/>
-      <c r="AT9" s="10">
+      <c r="AP9" s="10"/>
+      <c r="AQ9" s="11"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="11"/>
+      <c r="AT9" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU9" s="9">
+      <c r="AU9" s="10">
         <v>1.0</v>
       </c>
       <c r="AV9" s="6" t="s">
@@ -4020,7 +4028,7 @@
       <c r="C10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <v>45994.52711805556</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -4050,7 +4058,7 @@
       <c r="M10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="8">
         <v>46007.26055555556</v>
       </c>
       <c r="O10" s="1" t="s">
@@ -4101,7 +4109,7 @@
       <c r="AD10" s="1">
         <v>213013.0</v>
       </c>
-      <c r="AE10" s="8">
+      <c r="AE10" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF10" s="1">
@@ -4122,26 +4130,26 @@
       <c r="AK10" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AL10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM10" s="9" t="s">
+      <c r="AL10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM10" s="11"/>
+      <c r="AN10" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AN10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO10" s="10"/>
-      <c r="AP10" s="9" t="s">
+      <c r="AO10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP10" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ10" s="10"/>
-      <c r="AR10" s="10"/>
-      <c r="AS10" s="10"/>
-      <c r="AT10" s="10">
+      <c r="AQ10" s="11"/>
+      <c r="AR10" s="11"/>
+      <c r="AS10" s="11"/>
+      <c r="AT10" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU10" s="10">
+      <c r="AU10" s="11">
         <v>0.0</v>
       </c>
       <c r="AV10" s="6" t="s">
@@ -4177,7 +4185,7 @@
       <c r="C11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <v>45994.66978009259</v>
       </c>
       <c r="E11" s="1">
@@ -4207,7 +4215,7 @@
       <c r="M11" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="8">
         <v>45994.671793981484</v>
       </c>
       <c r="O11" s="1" t="s">
@@ -4258,7 +4266,7 @@
       <c r="AD11" s="1">
         <v>127576.0</v>
       </c>
-      <c r="AE11" s="8">
+      <c r="AE11" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF11" s="1">
@@ -4279,22 +4287,22 @@
       <c r="AK11" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="AL11" s="10"/>
-      <c r="AM11" s="10"/>
-      <c r="AN11" s="1" t="s">
+      <c r="AL11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AO11" s="10"/>
-      <c r="AP11" s="9" t="s">
+      <c r="AM11" s="11"/>
+      <c r="AN11" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ11" s="10"/>
-      <c r="AR11" s="10"/>
-      <c r="AS11" s="10"/>
-      <c r="AT11" s="10">
+      <c r="AO11" s="11"/>
+      <c r="AP11" s="11"/>
+      <c r="AQ11" s="11"/>
+      <c r="AR11" s="11"/>
+      <c r="AS11" s="11"/>
+      <c r="AT11" s="11">
         <v>4.0</v>
       </c>
-      <c r="AU11" s="10">
+      <c r="AU11" s="11">
         <v>0.0</v>
       </c>
       <c r="AV11" s="4" t="s">
@@ -4330,7 +4338,7 @@
       <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <v>45994.06568287037</v>
       </c>
       <c r="E12" s="1">
@@ -4360,7 +4368,7 @@
       <c r="M12" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="8">
         <v>46010.21131944445</v>
       </c>
       <c r="O12" s="1" t="s">
@@ -4411,7 +4419,7 @@
       <c r="AD12" s="1">
         <v>121963.0</v>
       </c>
-      <c r="AE12" s="8">
+      <c r="AE12" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF12" s="1">
@@ -4432,24 +4440,24 @@
       <c r="AK12" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AL12" s="4" t="s">
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="10"/>
+      <c r="AN12" s="10"/>
+      <c r="AO12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM12" s="9"/>
-      <c r="AN12" s="9"/>
-      <c r="AO12" s="9"/>
-      <c r="AP12" s="9"/>
-      <c r="AQ12" s="9" t="s">
+      <c r="AP12" s="10"/>
+      <c r="AQ12" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="AR12" s="9"/>
-      <c r="AS12" s="9" t="s">
+      <c r="AR12" s="10"/>
+      <c r="AS12" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT12" s="10">
+      <c r="AT12" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU12" s="9">
+      <c r="AU12" s="10">
         <v>1.0</v>
       </c>
       <c r="AV12" s="6" t="s">
@@ -4485,7 +4493,7 @@
       <c r="C13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <v>45994.56636574074</v>
       </c>
       <c r="E13" s="1">
@@ -4515,7 +4523,7 @@
       <c r="M13" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="8">
         <v>45994.57372685185</v>
       </c>
       <c r="O13" s="1" t="s">
@@ -4566,7 +4574,7 @@
       <c r="AD13" s="1">
         <v>55926.0</v>
       </c>
-      <c r="AE13" s="8">
+      <c r="AE13" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF13" s="1">
@@ -4587,12 +4595,12 @@
       <c r="AK13" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="AL13" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
-      <c r="AO13" s="1"/>
+      <c r="AO13" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1" t="s">
         <v>165</v>
@@ -4639,7 +4647,7 @@
       <c r="C14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <v>45994.11471064815</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -4669,7 +4677,7 @@
       <c r="M14" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="8">
         <v>45994.11675925926</v>
       </c>
       <c r="O14" s="1" t="s">
@@ -4720,7 +4728,7 @@
       <c r="AD14" s="1">
         <v>79969.0</v>
       </c>
-      <c r="AE14" s="8">
+      <c r="AE14" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF14" s="1">
@@ -4741,26 +4749,26 @@
       <c r="AK14" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AL14" s="4" t="s">
+      <c r="AL14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM14" s="11"/>
+      <c r="AN14" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AO14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM14" s="10"/>
-      <c r="AN14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO14" s="10"/>
-      <c r="AP14" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ14" s="9" t="s">
+      <c r="AP14" s="11"/>
+      <c r="AQ14" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="AR14" s="10"/>
-      <c r="AS14" s="10"/>
-      <c r="AT14" s="10">
+      <c r="AR14" s="11"/>
+      <c r="AS14" s="11"/>
+      <c r="AT14" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU14" s="10">
+      <c r="AU14" s="11">
         <v>2.0</v>
       </c>
       <c r="AV14" s="6" t="s">
@@ -4796,7 +4804,7 @@
       <c r="C15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <v>45995.563125</v>
       </c>
       <c r="E15" s="1">
@@ -4826,7 +4834,7 @@
       <c r="M15" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="8">
         <v>45995.56622685185</v>
       </c>
       <c r="O15" s="1" t="s">
@@ -4877,7 +4885,7 @@
       <c r="AD15" s="1">
         <v>71055.0</v>
       </c>
-      <c r="AE15" s="8">
+      <c r="AE15" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF15" s="1">
@@ -4898,17 +4906,17 @@
       <c r="AK15" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="AL15" s="4" t="s">
-        <v>41</v>
+      <c r="AL15" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO15" s="1"/>
-      <c r="AP15" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="AO15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP15" s="1"/>
       <c r="AQ15" s="1" t="s">
         <v>181</v>
       </c>
@@ -4954,7 +4962,7 @@
       <c r="C16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <v>45994.64262731482</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -4984,7 +4992,7 @@
       <c r="M16" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="8">
         <v>45994.65332175926</v>
       </c>
       <c r="O16" s="1" t="s">
@@ -5035,7 +5043,7 @@
       <c r="AD16" s="1">
         <v>53361.0</v>
       </c>
-      <c r="AE16" s="8">
+      <c r="AE16" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF16" s="1">
@@ -5056,12 +5064,12 @@
       <c r="AK16" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AL16" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1"/>
-      <c r="AO16" s="1"/>
+      <c r="AO16" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP16" s="1"/>
       <c r="AQ16" s="1" t="s">
         <v>192</v>
@@ -5111,7 +5119,7 @@
       <c r="C17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>45995.74130787037</v>
       </c>
       <c r="E17" s="1">
@@ -5141,7 +5149,7 @@
       <c r="M17" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N17" s="8">
         <v>45995.74935185185</v>
       </c>
       <c r="O17" s="1" t="s">
@@ -5192,7 +5200,7 @@
       <c r="AD17" s="1">
         <v>9204.0</v>
       </c>
-      <c r="AE17" s="8">
+      <c r="AE17" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF17" s="1">
@@ -5213,12 +5221,12 @@
       <c r="AK17" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AL17" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
-      <c r="AO17" s="1"/>
+      <c r="AO17" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1" t="s">
         <v>200</v>
@@ -5265,7 +5273,7 @@
       <c r="C18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <v>45995.02384259259</v>
       </c>
       <c r="E18" s="1">
@@ -5295,7 +5303,7 @@
       <c r="M18" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="N18" s="7">
+      <c r="N18" s="8">
         <v>46007.25508101852</v>
       </c>
       <c r="O18" s="1" t="s">
@@ -5346,7 +5354,7 @@
       <c r="AD18" s="1">
         <v>287567.0</v>
       </c>
-      <c r="AE18" s="8">
+      <c r="AE18" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF18" s="1">
@@ -5367,26 +5375,26 @@
       <c r="AK18" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="AL18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM18" s="9" t="s">
+      <c r="AL18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM18" s="11"/>
+      <c r="AN18" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AN18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO18" s="10"/>
-      <c r="AP18" s="9" t="s">
+      <c r="AO18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP18" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ18" s="9"/>
-      <c r="AR18" s="10"/>
-      <c r="AS18" s="10"/>
-      <c r="AT18" s="10">
+      <c r="AQ18" s="10"/>
+      <c r="AR18" s="11"/>
+      <c r="AS18" s="11"/>
+      <c r="AT18" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU18" s="10">
+      <c r="AU18" s="11">
         <v>0.0</v>
       </c>
       <c r="AV18" s="6" t="s">
@@ -5424,7 +5432,7 @@
       <c r="C19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>45995.98662037037</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -5454,7 +5462,7 @@
       <c r="M19" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="8">
         <v>45995.99244212963</v>
       </c>
       <c r="O19" s="1" t="s">
@@ -5505,7 +5513,7 @@
       <c r="AD19" s="1">
         <v>130764.0</v>
       </c>
-      <c r="AE19" s="8">
+      <c r="AE19" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF19" s="1">
@@ -5526,26 +5534,26 @@
       <c r="AK19" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AL19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM19" s="9" t="s">
+      <c r="AL19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM19" s="11"/>
+      <c r="AN19" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AN19" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO19" s="10"/>
-      <c r="AP19" s="9" t="s">
+      <c r="AO19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP19" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ19" s="10"/>
-      <c r="AR19" s="10"/>
-      <c r="AS19" s="10"/>
-      <c r="AT19" s="10">
+      <c r="AQ19" s="11"/>
+      <c r="AR19" s="11"/>
+      <c r="AS19" s="11"/>
+      <c r="AT19" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU19" s="10">
+      <c r="AU19" s="11">
         <v>0.0</v>
       </c>
       <c r="AV19" s="4" t="s">
@@ -5581,7 +5589,7 @@
       <c r="C20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>45994.66679398148</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -5611,7 +5619,7 @@
       <c r="M20" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="N20" s="7">
+      <c r="N20" s="8">
         <v>46031.11791666667</v>
       </c>
       <c r="O20" s="1" t="s">
@@ -5662,7 +5670,7 @@
       <c r="AD20" s="1">
         <v>134407.0</v>
       </c>
-      <c r="AE20" s="8">
+      <c r="AE20" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF20" s="1">
@@ -5683,22 +5691,22 @@
       <c r="AK20" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AL20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM20" s="9" t="s">
+      <c r="AL20" s="11"/>
+      <c r="AM20" s="11"/>
+      <c r="AN20" s="11"/>
+      <c r="AO20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP20" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AN20" s="10"/>
-      <c r="AO20" s="10"/>
-      <c r="AP20" s="10"/>
-      <c r="AQ20" s="10"/>
-      <c r="AR20" s="10"/>
-      <c r="AS20" s="10"/>
-      <c r="AT20" s="10">
+      <c r="AQ20" s="11"/>
+      <c r="AR20" s="11"/>
+      <c r="AS20" s="11"/>
+      <c r="AT20" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU20" s="10">
+      <c r="AU20" s="11">
         <v>0.0</v>
       </c>
       <c r="AV20" s="6" t="s">
@@ -5734,7 +5742,7 @@
       <c r="C21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <v>45994.98893518518</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -5764,7 +5772,7 @@
       <c r="M21" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="N21" s="7">
+      <c r="N21" s="8">
         <v>45994.99076388889</v>
       </c>
       <c r="O21" s="1" t="s">
@@ -5815,7 +5823,7 @@
       <c r="AD21" s="1">
         <v>54398.0</v>
       </c>
-      <c r="AE21" s="8">
+      <c r="AE21" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF21" s="1">
@@ -5836,22 +5844,22 @@
       <c r="AK21" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="AL21" s="10"/>
-      <c r="AM21" s="10"/>
-      <c r="AN21" s="1" t="s">
+      <c r="AL21" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AO21" s="10"/>
-      <c r="AP21" s="9" t="s">
+      <c r="AM21" s="11"/>
+      <c r="AN21" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ21" s="10"/>
-      <c r="AR21" s="10"/>
-      <c r="AS21" s="10"/>
-      <c r="AT21" s="10">
+      <c r="AO21" s="11"/>
+      <c r="AP21" s="11"/>
+      <c r="AQ21" s="11"/>
+      <c r="AR21" s="11"/>
+      <c r="AS21" s="11"/>
+      <c r="AT21" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU21" s="10">
+      <c r="AU21" s="11">
         <v>2.0</v>
       </c>
       <c r="AV21" s="6" t="s">
@@ -5887,7 +5895,7 @@
       <c r="C22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <v>45994.54665509259</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -5917,7 +5925,7 @@
       <c r="M22" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="N22" s="7">
+      <c r="N22" s="8">
         <v>45994.55337962963</v>
       </c>
       <c r="O22" s="1" t="s">
@@ -5968,7 +5976,7 @@
       <c r="AD22" s="1">
         <v>38142.0</v>
       </c>
-      <c r="AE22" s="8">
+      <c r="AE22" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF22" s="1">
@@ -5989,20 +5997,20 @@
       <c r="AK22" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="AL22" s="9"/>
-      <c r="AM22" s="9"/>
-      <c r="AN22" s="9"/>
-      <c r="AO22" s="9"/>
-      <c r="AP22" s="9"/>
-      <c r="AQ22" s="9"/>
-      <c r="AR22" s="9" t="s">
+      <c r="AL22" s="10"/>
+      <c r="AM22" s="10"/>
+      <c r="AN22" s="10"/>
+      <c r="AO22" s="10"/>
+      <c r="AP22" s="10"/>
+      <c r="AQ22" s="10"/>
+      <c r="AR22" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AS22" s="10"/>
-      <c r="AT22" s="10">
+      <c r="AS22" s="11"/>
+      <c r="AT22" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU22" s="10">
+      <c r="AU22" s="11">
         <v>2.0</v>
       </c>
       <c r="AV22" s="4" t="s">
@@ -6040,7 +6048,7 @@
       <c r="C23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <v>45994.55039351852</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -6070,7 +6078,7 @@
       <c r="M23" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="N23" s="7">
+      <c r="N23" s="8">
         <v>45994.55263888889</v>
       </c>
       <c r="O23" s="1" t="s">
@@ -6121,7 +6129,7 @@
       <c r="AD23" s="1">
         <v>84075.0</v>
       </c>
-      <c r="AE23" s="8">
+      <c r="AE23" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF23" s="1">
@@ -6142,16 +6150,16 @@
       <c r="AK23" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="AL23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM23" s="1" t="s">
+      <c r="AL23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM23" s="1"/>
+      <c r="AN23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AN23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO23" s="1"/>
+      <c r="AO23" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="AP23" s="1" t="s">
         <v>95</v>
       </c>
@@ -6196,7 +6204,7 @@
       <c r="C24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="8">
         <v>45995.74737268518</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -6226,7 +6234,7 @@
       <c r="M24" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="8">
         <v>45995.75577546296</v>
       </c>
       <c r="O24" s="1" t="s">
@@ -6277,7 +6285,7 @@
       <c r="AD24" s="1">
         <v>27954.0</v>
       </c>
-      <c r="AE24" s="8">
+      <c r="AE24" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF24" s="1">
@@ -6344,7 +6352,7 @@
       <c r="C25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <v>45995.812268518515</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -6374,7 +6382,7 @@
       <c r="M25" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="N25" s="7">
+      <c r="N25" s="8">
         <v>45995.82402777778</v>
       </c>
       <c r="O25" s="1" t="s">
@@ -6425,7 +6433,7 @@
       <c r="AD25" s="1">
         <v>24981.0</v>
       </c>
-      <c r="AE25" s="8">
+      <c r="AE25" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF25" s="1">
@@ -6446,15 +6454,15 @@
       <c r="AK25" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="AL25" s="4"/>
+      <c r="AL25" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="AM25" s="1"/>
       <c r="AN25" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO25" s="1"/>
-      <c r="AP25" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="AO25" s="4"/>
+      <c r="AP25" s="1"/>
       <c r="AQ25" s="1"/>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
@@ -6496,7 +6504,7 @@
       <c r="C26" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="8">
         <v>45995.010625</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -6526,7 +6534,7 @@
       <c r="M26" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="N26" s="7">
+      <c r="N26" s="8">
         <v>45995.02144675926</v>
       </c>
       <c r="O26" s="1" t="s">
@@ -6577,7 +6585,7 @@
       <c r="AD26" s="1">
         <v>33762.0</v>
       </c>
-      <c r="AE26" s="8">
+      <c r="AE26" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF26" s="1">
@@ -6598,15 +6606,15 @@
       <c r="AK26" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="AL26" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM26" s="1" t="s">
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP26" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AN26" s="1"/>
-      <c r="AO26" s="1"/>
-      <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
       <c r="AR26" s="1"/>
       <c r="AS26" s="1"/>
@@ -6651,7 +6659,7 @@
       <c r="C27" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <v>45995.11435185185</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -6681,7 +6689,7 @@
       <c r="M27" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="8">
         <v>45996.700474537036</v>
       </c>
       <c r="O27" s="1" t="s">
@@ -6732,7 +6740,7 @@
       <c r="AD27" s="1">
         <v>25560.0</v>
       </c>
-      <c r="AE27" s="8">
+      <c r="AE27" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF27" s="1">
@@ -6753,14 +6761,14 @@
       <c r="AK27" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="AL27" s="1"/>
-      <c r="AM27" s="1"/>
-      <c r="AN27" s="1" t="s">
+      <c r="AL27" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AO27" s="1" t="s">
+      <c r="AM27" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="AN27" s="1"/>
+      <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
       <c r="AQ27" s="1"/>
       <c r="AR27" s="1"/>
@@ -6803,7 +6811,7 @@
       <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <v>45995.59412037037</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -6833,7 +6841,7 @@
       <c r="M28" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="8">
         <v>45997.006203703706</v>
       </c>
       <c r="O28" s="1" t="s">
@@ -6884,7 +6892,7 @@
       <c r="AD28" s="1">
         <v>16292.0</v>
       </c>
-      <c r="AE28" s="8">
+      <c r="AE28" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF28" s="1">
@@ -6905,19 +6913,19 @@
       <c r="AK28" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="AL28" s="4" t="s">
-        <v>37</v>
+      <c r="AL28" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="AM28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AN28" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO28" s="1" t="s">
+      <c r="AN28" s="1"/>
+      <c r="AO28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AP28" s="1"/>
       <c r="AQ28" s="1"/>
       <c r="AR28" s="1"/>
       <c r="AS28" s="1" t="s">
@@ -6961,7 +6969,7 @@
       <c r="C29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <v>45994.60083333333</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -6991,7 +6999,7 @@
       <c r="M29" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="N29" s="7">
+      <c r="N29" s="8">
         <v>45998.15046296296</v>
       </c>
       <c r="O29" s="1" t="s">
@@ -7042,7 +7050,7 @@
       <c r="AD29" s="1">
         <v>15295.0</v>
       </c>
-      <c r="AE29" s="8">
+      <c r="AE29" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF29" s="1">
@@ -7063,16 +7071,16 @@
       <c r="AK29" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="AL29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM29" s="1" t="s">
+      <c r="AL29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AN29" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO29" s="1"/>
+      <c r="AO29" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="AP29" s="1" t="s">
         <v>110</v>
       </c>
@@ -7117,7 +7125,7 @@
       <c r="C30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <v>45995.54997685185</v>
       </c>
       <c r="E30" s="1">
@@ -7147,7 +7155,7 @@
       <c r="M30" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="N30" s="7">
+      <c r="N30" s="8">
         <v>45995.5665625</v>
       </c>
       <c r="O30" s="1" t="s">
@@ -7198,7 +7206,7 @@
       <c r="AD30" s="1">
         <v>25702.0</v>
       </c>
-      <c r="AE30" s="8">
+      <c r="AE30" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF30" s="1">
@@ -7219,19 +7227,19 @@
       <c r="AK30" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="AL30" s="4" t="s">
-        <v>37</v>
+      <c r="AL30" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="AM30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AN30" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO30" s="1" t="s">
+      <c r="AN30" s="1"/>
+      <c r="AO30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AP30" s="1"/>
       <c r="AQ30" s="1"/>
       <c r="AR30" s="1"/>
       <c r="AS30" s="1"/>
@@ -7273,7 +7281,7 @@
       <c r="C31" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <v>45995.54814814815</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -7303,7 +7311,7 @@
       <c r="M31" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="N31" s="7">
+      <c r="N31" s="8">
         <v>45995.62306712963</v>
       </c>
       <c r="O31" s="1" t="s">
@@ -7354,7 +7362,7 @@
       <c r="AD31" s="1">
         <v>20833.0</v>
       </c>
-      <c r="AE31" s="8">
+      <c r="AE31" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF31" s="1">
@@ -7375,15 +7383,15 @@
       <c r="AK31" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="AL31" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM31" s="1" t="s">
+      <c r="AL31" s="1"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+      <c r="AO31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AN31" s="1"/>
-      <c r="AO31" s="1"/>
-      <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
       <c r="AR31" s="1"/>
       <c r="AS31" s="1"/>
@@ -7425,7 +7433,7 @@
       <c r="C32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="8">
         <v>45994.93221064815</v>
       </c>
       <c r="E32" s="1">
@@ -7455,7 +7463,7 @@
       <c r="M32" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="N32" s="7">
+      <c r="N32" s="8">
         <v>45994.94862268519</v>
       </c>
       <c r="O32" s="1" t="s">
@@ -7506,7 +7514,7 @@
       <c r="AD32" s="1">
         <v>9247.0</v>
       </c>
-      <c r="AE32" s="8">
+      <c r="AE32" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF32" s="1">
@@ -7527,16 +7535,16 @@
       <c r="AK32" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AL32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM32" s="1" t="s">
+      <c r="AL32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AN32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO32" s="1"/>
+      <c r="AO32" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="AP32" s="1" t="s">
         <v>95</v>
       </c>
@@ -7581,7 +7589,7 @@
       <c r="C33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <v>45995.8696412037</v>
       </c>
       <c r="E33" s="1">
@@ -7611,7 +7619,7 @@
       <c r="M33" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="N33" s="7">
+      <c r="N33" s="8">
         <v>46057.48789351852</v>
       </c>
       <c r="O33" s="1" t="s">
@@ -7662,7 +7670,7 @@
       <c r="AD33" s="1">
         <v>9884.0</v>
       </c>
-      <c r="AE33" s="8">
+      <c r="AE33" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF33" s="1">
@@ -7683,15 +7691,15 @@
       <c r="AK33" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AL33" s="1"/>
+      <c r="AL33" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="AM33" s="1"/>
       <c r="AN33" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO33" s="1"/>
-      <c r="AP33" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
       <c r="AR33" s="1"/>
       <c r="AS33" s="1"/>
@@ -7733,7 +7741,7 @@
       <c r="C34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="8">
         <v>45995.701053240744</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -7763,7 +7771,7 @@
       <c r="M34" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="N34" s="7">
+      <c r="N34" s="8">
         <v>45995.70224537037</v>
       </c>
       <c r="O34" s="1" t="s">
@@ -7814,7 +7822,7 @@
       <c r="AD34" s="1">
         <v>10709.0</v>
       </c>
-      <c r="AE34" s="8">
+      <c r="AE34" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF34" s="1">
@@ -7835,15 +7843,15 @@
       <c r="AK34" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AL34" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM34" s="1" t="s">
+      <c r="AL34" s="1"/>
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="1"/>
+      <c r="AO34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP34" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AN34" s="1"/>
-      <c r="AO34" s="1"/>
-      <c r="AP34" s="1"/>
       <c r="AQ34" s="1"/>
       <c r="AR34" s="1" t="s">
         <v>173</v>
@@ -7887,7 +7895,7 @@
       <c r="C35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="8">
         <v>45994.79645833333</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -7917,7 +7925,7 @@
       <c r="M35" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="N35" s="7">
+      <c r="N35" s="8">
         <v>45994.80432870371</v>
       </c>
       <c r="O35" s="1" t="s">
@@ -7968,7 +7976,7 @@
       <c r="AD35" s="1">
         <v>9031.0</v>
       </c>
-      <c r="AE35" s="8">
+      <c r="AE35" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF35" s="1">
@@ -7989,14 +7997,14 @@
       <c r="AK35" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AL35" s="1"/>
-      <c r="AM35" s="1"/>
-      <c r="AN35" s="1" t="s">
+      <c r="AL35" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AO35" s="1" t="s">
+      <c r="AM35" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="AN35" s="1"/>
+      <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
       <c r="AR35" s="1"/>
@@ -8039,7 +8047,7 @@
       <c r="C36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="8">
         <v>45995.44997685185</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -8069,7 +8077,7 @@
       <c r="M36" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="N36" s="7">
+      <c r="N36" s="8">
         <v>45995.456712962965</v>
       </c>
       <c r="O36" s="1" t="s">
@@ -8120,7 +8128,7 @@
       <c r="AD36" s="1">
         <v>35843.0</v>
       </c>
-      <c r="AE36" s="8">
+      <c r="AE36" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF36" s="1">
@@ -8187,7 +8195,7 @@
       <c r="C37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="8">
         <v>45994.525613425925</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -8217,7 +8225,7 @@
       <c r="M37" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="N37" s="7">
+      <c r="N37" s="8">
         <v>46011.05478009259</v>
       </c>
       <c r="O37" s="1" t="s">
@@ -8268,7 +8276,7 @@
       <c r="AD37" s="1">
         <v>77755.0</v>
       </c>
-      <c r="AE37" s="8">
+      <c r="AE37" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF37" s="1">
@@ -8289,12 +8297,12 @@
       <c r="AK37" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="AL37" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
       <c r="AN37" s="1"/>
-      <c r="AO37" s="1"/>
+      <c r="AO37" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1" t="s">
         <v>165</v>
@@ -8341,7 +8349,7 @@
       <c r="C38" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="8">
         <v>45994.551782407405</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -8371,7 +8379,7 @@
       <c r="M38" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="N38" s="7">
+      <c r="N38" s="8">
         <v>45994.55981481481</v>
       </c>
       <c r="O38" s="1" t="s">
@@ -8422,7 +8430,7 @@
       <c r="AD38" s="1">
         <v>138493.0</v>
       </c>
-      <c r="AE38" s="8">
+      <c r="AE38" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF38" s="1">
@@ -8443,12 +8451,12 @@
       <c r="AK38" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="AL38" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL38" s="1"/>
       <c r="AM38" s="1"/>
       <c r="AN38" s="1"/>
-      <c r="AO38" s="1"/>
+      <c r="AO38" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP38" s="1"/>
       <c r="AQ38" s="1" t="s">
         <v>165</v>
@@ -8495,7 +8503,7 @@
       <c r="C39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="8">
         <v>45994.6408912037</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -8525,7 +8533,7 @@
       <c r="M39" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="N39" s="7">
+      <c r="N39" s="8">
         <v>45995.00494212963</v>
       </c>
       <c r="O39" s="1" t="s">
@@ -8576,7 +8584,7 @@
       <c r="AD39" s="1">
         <v>14933.0</v>
       </c>
-      <c r="AE39" s="8">
+      <c r="AE39" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF39" s="1">
@@ -8597,12 +8605,12 @@
       <c r="AK39" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="AL39" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
       <c r="AN39" s="1"/>
-      <c r="AO39" s="1"/>
+      <c r="AO39" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1" t="s">
         <v>165</v>
@@ -8649,7 +8657,7 @@
       <c r="C40" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="8">
         <v>45994.514861111114</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -8679,7 +8687,7 @@
       <c r="M40" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="N40" s="7">
+      <c r="N40" s="8">
         <v>45994.51818287037</v>
       </c>
       <c r="O40" s="1" t="s">
@@ -8730,7 +8738,7 @@
       <c r="AD40" s="1">
         <v>55483.0</v>
       </c>
-      <c r="AE40" s="8">
+      <c r="AE40" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF40" s="1">
@@ -8751,12 +8759,12 @@
       <c r="AK40" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="AL40" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
       <c r="AN40" s="1"/>
-      <c r="AO40" s="1"/>
+      <c r="AO40" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP40" s="1"/>
       <c r="AQ40" s="1" t="s">
         <v>165</v>
@@ -8805,7 +8813,7 @@
       <c r="C41" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="8">
         <v>45994.52579861111</v>
       </c>
       <c r="E41" s="1">
@@ -8835,7 +8843,7 @@
       <c r="M41" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="N41" s="7">
+      <c r="N41" s="8">
         <v>45994.5356712963</v>
       </c>
       <c r="O41" s="1" t="s">
@@ -8886,7 +8894,7 @@
       <c r="AD41" s="1">
         <v>55391.0</v>
       </c>
-      <c r="AE41" s="8">
+      <c r="AE41" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF41" s="1">
@@ -8907,12 +8915,12 @@
       <c r="AK41" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="AL41" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
       <c r="AN41" s="1"/>
-      <c r="AO41" s="1"/>
+      <c r="AO41" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP41" s="1"/>
       <c r="AQ41" s="1" t="s">
         <v>165</v>
@@ -8959,7 +8967,7 @@
       <c r="C42" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="8">
         <v>45994.06253472222</v>
       </c>
       <c r="E42" s="1">
@@ -8989,7 +8997,7 @@
       <c r="M42" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="N42" s="7">
+      <c r="N42" s="8">
         <v>45994.06482638889</v>
       </c>
       <c r="O42" s="1" t="s">
@@ -9040,7 +9048,7 @@
       <c r="AD42" s="1">
         <v>281299.0</v>
       </c>
-      <c r="AE42" s="8">
+      <c r="AE42" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF42" s="1">
@@ -9061,28 +9069,28 @@
       <c r="AK42" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="AL42" s="4" t="s">
+      <c r="AL42" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM42" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN42" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM42" s="9"/>
-      <c r="AN42" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO42" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP42" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ42" s="9" t="s">
+      <c r="AP42" s="10"/>
+      <c r="AQ42" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="AR42" s="10"/>
-      <c r="AS42" s="10"/>
-      <c r="AT42" s="9">
+      <c r="AR42" s="11"/>
+      <c r="AS42" s="11"/>
+      <c r="AT42" s="10">
         <v>2.0</v>
       </c>
-      <c r="AU42" s="10">
+      <c r="AU42" s="11">
         <v>2.0</v>
       </c>
       <c r="AV42" s="6" t="s">
@@ -9118,7 +9126,7 @@
       <c r="C43" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="8">
         <v>45994.73105324074</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -9148,7 +9156,7 @@
       <c r="M43" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="N43" s="7">
+      <c r="N43" s="8">
         <v>45994.73297453704</v>
       </c>
       <c r="O43" s="1" t="s">
@@ -9199,7 +9207,7 @@
       <c r="AD43" s="1">
         <v>355116.0</v>
       </c>
-      <c r="AE43" s="8">
+      <c r="AE43" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF43" s="1">
@@ -9220,28 +9228,28 @@
       <c r="AK43" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="AL43" s="4" t="s">
+      <c r="AL43" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM43" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN43" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO43" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM43" s="9"/>
-      <c r="AN43" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO43" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP43" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ43" s="9" t="s">
+      <c r="AP43" s="10"/>
+      <c r="AQ43" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="AR43" s="10"/>
-      <c r="AS43" s="10"/>
-      <c r="AT43" s="9">
+      <c r="AR43" s="11"/>
+      <c r="AS43" s="11"/>
+      <c r="AT43" s="10">
         <v>2.0</v>
       </c>
-      <c r="AU43" s="10">
+      <c r="AU43" s="11">
         <v>2.0</v>
       </c>
       <c r="AV43" s="6" t="s">
@@ -9279,7 +9287,7 @@
       <c r="C44" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="8">
         <v>45994.6394212963</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -9309,7 +9317,7 @@
       <c r="M44" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="N44" s="7">
+      <c r="N44" s="8">
         <v>45995.17346064815</v>
       </c>
       <c r="O44" s="1" t="s">
@@ -9360,7 +9368,7 @@
       <c r="AD44" s="1">
         <v>69620.0</v>
       </c>
-      <c r="AE44" s="8">
+      <c r="AE44" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF44" s="1">
@@ -9381,24 +9389,24 @@
       <c r="AK44" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="AL44" s="4" t="s">
+      <c r="AL44" s="10"/>
+      <c r="AM44" s="10"/>
+      <c r="AN44" s="10"/>
+      <c r="AO44" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM44" s="9"/>
-      <c r="AN44" s="9"/>
-      <c r="AO44" s="9"/>
-      <c r="AP44" s="9"/>
-      <c r="AQ44" s="9" t="s">
+      <c r="AP44" s="10"/>
+      <c r="AQ44" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="AR44" s="9"/>
-      <c r="AS44" s="9" t="s">
+      <c r="AR44" s="10"/>
+      <c r="AS44" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AT44" s="9">
+      <c r="AT44" s="10">
         <v>1.0</v>
       </c>
-      <c r="AU44" s="10">
+      <c r="AU44" s="11">
         <v>2.0</v>
       </c>
       <c r="AV44" s="4" t="s">
@@ -9434,7 +9442,7 @@
       <c r="C45" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="8">
         <v>45994.513969907406</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -9464,7 +9472,7 @@
       <c r="M45" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="N45" s="7">
+      <c r="N45" s="8">
         <v>46007.2622337963</v>
       </c>
       <c r="O45" s="1" t="s">
@@ -9515,7 +9523,7 @@
       <c r="AD45" s="1">
         <v>274182.0</v>
       </c>
-      <c r="AE45" s="8">
+      <c r="AE45" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF45" s="1">
@@ -9536,24 +9544,24 @@
       <c r="AK45" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="AL45" s="4" t="s">
+      <c r="AL45" s="10"/>
+      <c r="AM45" s="10"/>
+      <c r="AN45" s="10"/>
+      <c r="AO45" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM45" s="9"/>
-      <c r="AN45" s="9"/>
-      <c r="AO45" s="9"/>
-      <c r="AP45" s="9"/>
-      <c r="AQ45" s="11" t="s">
+      <c r="AP45" s="10"/>
+      <c r="AQ45" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="AR45" s="9" t="s">
+      <c r="AR45" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AS45" s="10"/>
-      <c r="AT45" s="9">
+      <c r="AS45" s="11"/>
+      <c r="AT45" s="10">
         <v>3.0</v>
       </c>
-      <c r="AU45" s="10">
+      <c r="AU45" s="11">
         <v>2.0</v>
       </c>
       <c r="AV45" s="6" t="s">
@@ -9591,7 +9599,7 @@
       <c r="C46" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="8">
         <v>45994.49744212963</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -9621,7 +9629,7 @@
       <c r="M46" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="N46" s="7">
+      <c r="N46" s="8">
         <v>45994.50645833334</v>
       </c>
       <c r="O46" s="1" t="s">
@@ -9672,7 +9680,7 @@
       <c r="AD46" s="1">
         <v>42203.0</v>
       </c>
-      <c r="AE46" s="8">
+      <c r="AE46" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF46" s="1">
@@ -9693,22 +9701,22 @@
       <c r="AK46" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="AL46" s="4" t="s">
+      <c r="AL46" s="11"/>
+      <c r="AM46" s="11"/>
+      <c r="AN46" s="11"/>
+      <c r="AO46" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM46" s="10"/>
-      <c r="AN46" s="10"/>
-      <c r="AO46" s="10"/>
-      <c r="AP46" s="10"/>
-      <c r="AQ46" s="11" t="s">
+      <c r="AP46" s="11"/>
+      <c r="AQ46" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="AR46" s="10"/>
-      <c r="AS46" s="10"/>
-      <c r="AT46" s="10">
+      <c r="AR46" s="11"/>
+      <c r="AS46" s="11"/>
+      <c r="AT46" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU46" s="10">
+      <c r="AU46" s="11">
         <v>2.0</v>
       </c>
       <c r="AV46" s="6" t="s">
@@ -9744,7 +9752,7 @@
       <c r="C47" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="8">
         <v>45994.530636574076</v>
       </c>
       <c r="E47" s="1">
@@ -9774,7 +9782,7 @@
       <c r="M47" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="N47" s="7">
+      <c r="N47" s="8">
         <v>46056.30416666667</v>
       </c>
       <c r="O47" s="1" t="s">
@@ -9825,7 +9833,7 @@
       <c r="AD47" s="1">
         <v>497755.0</v>
       </c>
-      <c r="AE47" s="8">
+      <c r="AE47" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF47" s="1">
@@ -9846,24 +9854,24 @@
       <c r="AK47" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="AL47" s="4" t="s">
+      <c r="AL47" s="10"/>
+      <c r="AM47" s="10"/>
+      <c r="AN47" s="10"/>
+      <c r="AO47" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM47" s="9"/>
-      <c r="AN47" s="9"/>
-      <c r="AO47" s="9"/>
-      <c r="AP47" s="9"/>
-      <c r="AQ47" s="9" t="s">
+      <c r="AP47" s="10"/>
+      <c r="AQ47" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="AR47" s="9"/>
-      <c r="AS47" s="9" t="s">
+      <c r="AR47" s="10"/>
+      <c r="AS47" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT47" s="10">
+      <c r="AT47" s="11">
         <v>0.0</v>
       </c>
-      <c r="AU47" s="9">
+      <c r="AU47" s="10">
         <v>1.0</v>
       </c>
       <c r="AV47" s="4" t="s">
@@ -9899,7 +9907,7 @@
       <c r="C48" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="8">
         <v>45994.605162037034</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -9929,7 +9937,7 @@
       <c r="M48" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="N48" s="7">
+      <c r="N48" s="8">
         <v>45994.606828703705</v>
       </c>
       <c r="O48" s="1" t="s">
@@ -9980,7 +9988,7 @@
       <c r="AD48" s="1">
         <v>534887.0</v>
       </c>
-      <c r="AE48" s="8">
+      <c r="AE48" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF48" s="1">
@@ -10001,24 +10009,24 @@
       <c r="AK48" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="AL48" s="4" t="s">
+      <c r="AL48" s="10"/>
+      <c r="AM48" s="10"/>
+      <c r="AN48" s="10"/>
+      <c r="AO48" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM48" s="9"/>
-      <c r="AN48" s="9"/>
-      <c r="AO48" s="9"/>
-      <c r="AP48" s="9"/>
-      <c r="AQ48" s="9" t="s">
+      <c r="AP48" s="10"/>
+      <c r="AQ48" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="AR48" s="9"/>
-      <c r="AS48" s="9" t="s">
+      <c r="AR48" s="10"/>
+      <c r="AS48" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT48" s="10">
+      <c r="AT48" s="11">
         <v>1.0</v>
       </c>
-      <c r="AU48" s="10">
+      <c r="AU48" s="11">
         <v>2.0</v>
       </c>
       <c r="AV48" s="6" t="s">
@@ -10054,7 +10062,7 @@
       <c r="C49" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="8">
         <v>45994.50971064815</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -10084,7 +10092,7 @@
       <c r="M49" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="N49" s="7">
+      <c r="N49" s="8">
         <v>46146.53533564815</v>
       </c>
       <c r="O49" s="1" t="s">
@@ -10135,7 +10143,7 @@
       <c r="AD49" s="1">
         <v>344481.0</v>
       </c>
-      <c r="AE49" s="8">
+      <c r="AE49" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF49" s="1">
@@ -10156,24 +10164,24 @@
       <c r="AK49" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="AL49" s="4" t="s">
+      <c r="AL49" s="10"/>
+      <c r="AM49" s="10"/>
+      <c r="AN49" s="10"/>
+      <c r="AO49" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM49" s="9"/>
-      <c r="AN49" s="9"/>
-      <c r="AO49" s="9"/>
-      <c r="AP49" s="9"/>
-      <c r="AQ49" s="9" t="s">
+      <c r="AP49" s="10"/>
+      <c r="AQ49" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="AR49" s="9"/>
-      <c r="AS49" s="9" t="s">
+      <c r="AR49" s="10"/>
+      <c r="AS49" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT49" s="10">
+      <c r="AT49" s="11">
         <v>0.0</v>
       </c>
-      <c r="AU49" s="10">
+      <c r="AU49" s="11">
         <v>2.0</v>
       </c>
       <c r="AV49" s="4" t="s">
@@ -10211,7 +10219,7 @@
       <c r="C50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="8">
         <v>45994.73488425926</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -10241,7 +10249,7 @@
       <c r="M50" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="N50" s="7">
+      <c r="N50" s="8">
         <v>45994.74375</v>
       </c>
       <c r="O50" s="1" t="s">
@@ -10292,7 +10300,7 @@
       <c r="AD50" s="1">
         <v>72121.0</v>
       </c>
-      <c r="AE50" s="8">
+      <c r="AE50" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF50" s="1">
@@ -10313,24 +10321,24 @@
       <c r="AK50" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="AL50" s="4" t="s">
+      <c r="AL50" s="10"/>
+      <c r="AM50" s="10"/>
+      <c r="AN50" s="10"/>
+      <c r="AO50" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM50" s="9"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="9"/>
-      <c r="AP50" s="9"/>
-      <c r="AQ50" s="9" t="s">
+      <c r="AP50" s="10"/>
+      <c r="AQ50" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="AR50" s="9" t="s">
+      <c r="AR50" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AS50" s="10"/>
-      <c r="AT50" s="9">
+      <c r="AS50" s="11"/>
+      <c r="AT50" s="10">
         <v>3.0</v>
       </c>
-      <c r="AU50" s="9">
+      <c r="AU50" s="10">
         <v>2.0</v>
       </c>
       <c r="AV50" s="4" t="s">
@@ -10368,7 +10376,7 @@
       <c r="C51" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="8">
         <v>45994.58121527778</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -10398,7 +10406,7 @@
       <c r="M51" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="N51" s="7">
+      <c r="N51" s="8">
         <v>45994.60625</v>
       </c>
       <c r="O51" s="1" t="s">
@@ -10449,7 +10457,7 @@
       <c r="AD51" s="1">
         <v>230295.0</v>
       </c>
-      <c r="AE51" s="8">
+      <c r="AE51" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF51" s="1">
@@ -10470,24 +10478,24 @@
       <c r="AK51" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="AL51" s="4" t="s">
+      <c r="AL51" s="10"/>
+      <c r="AM51" s="10"/>
+      <c r="AN51" s="10"/>
+      <c r="AO51" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM51" s="9"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="9"/>
-      <c r="AP51" s="9"/>
-      <c r="AQ51" s="9" t="s">
+      <c r="AP51" s="10"/>
+      <c r="AQ51" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="AR51" s="9"/>
-      <c r="AS51" s="9" t="s">
+      <c r="AR51" s="10"/>
+      <c r="AS51" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT51" s="10">
+      <c r="AT51" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU51" s="10">
+      <c r="AU51" s="11">
         <v>2.0</v>
       </c>
       <c r="AV51" s="4" t="s">
@@ -10525,7 +10533,7 @@
       <c r="C52" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="8">
         <v>45994.68853009259</v>
       </c>
       <c r="E52" s="1">
@@ -10555,7 +10563,7 @@
       <c r="M52" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="N52" s="7">
+      <c r="N52" s="8">
         <v>45994.689837962964</v>
       </c>
       <c r="O52" s="1" t="s">
@@ -10606,7 +10614,7 @@
       <c r="AD52" s="1">
         <v>204559.0</v>
       </c>
-      <c r="AE52" s="8">
+      <c r="AE52" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF52" s="1">
@@ -10627,24 +10635,24 @@
       <c r="AK52" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="AL52" s="4" t="s">
+      <c r="AL52" s="10"/>
+      <c r="AM52" s="10"/>
+      <c r="AN52" s="10"/>
+      <c r="AO52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM52" s="9"/>
-      <c r="AN52" s="9"/>
-      <c r="AO52" s="9"/>
-      <c r="AP52" s="9"/>
-      <c r="AQ52" s="9" t="s">
+      <c r="AP52" s="10"/>
+      <c r="AQ52" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="AR52" s="9"/>
-      <c r="AS52" s="9" t="s">
+      <c r="AR52" s="10"/>
+      <c r="AS52" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT52" s="10">
+      <c r="AT52" s="11">
         <v>1.0</v>
       </c>
-      <c r="AU52" s="10">
+      <c r="AU52" s="11">
         <v>2.0</v>
       </c>
       <c r="AV52" s="4" t="s">
@@ -10682,7 +10690,7 @@
       <c r="C53" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="8">
         <v>45995.429247685184</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -10712,7 +10720,7 @@
       <c r="M53" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="N53" s="7">
+      <c r="N53" s="8">
         <v>45995.43769675926</v>
       </c>
       <c r="O53" s="1" t="s">
@@ -10763,7 +10771,7 @@
       <c r="AD53" s="1">
         <v>58193.0</v>
       </c>
-      <c r="AE53" s="8">
+      <c r="AE53" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF53" s="1">
@@ -10784,24 +10792,24 @@
       <c r="AK53" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="AL53" s="4" t="s">
+      <c r="AL53" s="10"/>
+      <c r="AM53" s="10"/>
+      <c r="AN53" s="10"/>
+      <c r="AO53" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM53" s="9"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="9"/>
-      <c r="AP53" s="9"/>
-      <c r="AQ53" s="9" t="s">
+      <c r="AP53" s="10"/>
+      <c r="AQ53" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="AR53" s="9"/>
-      <c r="AS53" s="9" t="s">
+      <c r="AR53" s="10"/>
+      <c r="AS53" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT53" s="10">
+      <c r="AT53" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU53" s="10">
+      <c r="AU53" s="11">
         <v>2.0</v>
       </c>
       <c r="AV53" s="6" t="s">
@@ -10839,7 +10847,7 @@
       <c r="C54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="8">
         <v>45994.618842592594</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -10869,7 +10877,7 @@
       <c r="M54" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="N54" s="7">
+      <c r="N54" s="8">
         <v>45994.624386574076</v>
       </c>
       <c r="O54" s="1" t="s">
@@ -10920,7 +10928,7 @@
       <c r="AD54" s="1">
         <v>30374.0</v>
       </c>
-      <c r="AE54" s="8">
+      <c r="AE54" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF54" s="1">
@@ -10941,18 +10949,18 @@
       <c r="AK54" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="AL54" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1"/>
-      <c r="AO54" s="1"/>
+      <c r="AO54" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP54" s="1"/>
       <c r="AQ54" s="1" t="s">
         <v>422</v>
       </c>
       <c r="AR54" s="1"/>
-      <c r="AS54" s="9" t="s">
+      <c r="AS54" s="10" t="s">
         <v>95</v>
       </c>
       <c r="AT54" s="1">
@@ -10996,7 +11004,7 @@
       <c r="C55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="8">
         <v>45994.51646990741</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -11026,7 +11034,7 @@
       <c r="M55" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="N55" s="7">
+      <c r="N55" s="8">
         <v>46056.242997685185</v>
       </c>
       <c r="O55" s="1" t="s">
@@ -11077,7 +11085,7 @@
       <c r="AD55" s="1">
         <v>107629.0</v>
       </c>
-      <c r="AE55" s="8">
+      <c r="AE55" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF55" s="1">
@@ -11098,22 +11106,22 @@
       <c r="AK55" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="AL55" s="9"/>
-      <c r="AM55" s="9"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="9"/>
-      <c r="AP55" s="9"/>
-      <c r="AQ55" s="9" t="s">
+      <c r="AL55" s="10"/>
+      <c r="AM55" s="10"/>
+      <c r="AN55" s="10"/>
+      <c r="AO55" s="10"/>
+      <c r="AP55" s="10"/>
+      <c r="AQ55" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AR55" s="9" t="s">
+      <c r="AR55" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AS55" s="10"/>
-      <c r="AT55" s="10">
+      <c r="AS55" s="11"/>
+      <c r="AT55" s="11">
         <v>1.0</v>
       </c>
-      <c r="AU55" s="10">
+      <c r="AU55" s="11">
         <v>1.0</v>
       </c>
       <c r="AV55" s="4" t="s">
@@ -11149,7 +11157,7 @@
       <c r="C56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="8">
         <v>45994.53223379629</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -11179,7 +11187,7 @@
       <c r="M56" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="N56" s="7">
+      <c r="N56" s="8">
         <v>45994.542395833334</v>
       </c>
       <c r="O56" s="1" t="s">
@@ -11230,7 +11238,7 @@
       <c r="AD56" s="1">
         <v>16815.0</v>
       </c>
-      <c r="AE56" s="8">
+      <c r="AE56" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF56" s="1">
@@ -11251,12 +11259,12 @@
       <c r="AK56" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="AL56" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
       <c r="AN56" s="1"/>
-      <c r="AO56" s="1"/>
+      <c r="AO56" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP56" s="1"/>
       <c r="AQ56" s="1" t="s">
         <v>96</v>
@@ -11303,7 +11311,7 @@
       <c r="C57" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="8">
         <v>45995.802928240744</v>
       </c>
       <c r="E57" s="1">
@@ -11333,7 +11341,7 @@
       <c r="M57" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="N57" s="7">
+      <c r="N57" s="8">
         <v>45995.80519675926</v>
       </c>
       <c r="O57" s="1" t="s">
@@ -11384,7 +11392,7 @@
       <c r="AD57" s="1">
         <v>118760.0</v>
       </c>
-      <c r="AE57" s="8">
+      <c r="AE57" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF57" s="1">
@@ -11405,24 +11413,24 @@
       <c r="AK57" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="AL57" s="4" t="s">
+      <c r="AL57" s="10"/>
+      <c r="AM57" s="10"/>
+      <c r="AN57" s="10"/>
+      <c r="AO57" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM57" s="9"/>
-      <c r="AN57" s="9"/>
-      <c r="AO57" s="9"/>
-      <c r="AP57" s="9"/>
-      <c r="AQ57" s="9" t="s">
+      <c r="AP57" s="10"/>
+      <c r="AQ57" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="AR57" s="9" t="s">
+      <c r="AR57" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="AS57" s="10"/>
-      <c r="AT57" s="10">
+      <c r="AS57" s="11"/>
+      <c r="AT57" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU57" s="10">
+      <c r="AU57" s="11">
         <v>2.0</v>
       </c>
       <c r="AV57" s="4" t="s">
@@ -11460,7 +11468,7 @@
       <c r="C58" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="8">
         <v>45994.55587962963</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -11490,7 +11498,7 @@
       <c r="M58" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="N58" s="7">
+      <c r="N58" s="8">
         <v>45994.57141203704</v>
       </c>
       <c r="O58" s="1" t="s">
@@ -11541,7 +11549,7 @@
       <c r="AD58" s="1">
         <v>74942.0</v>
       </c>
-      <c r="AE58" s="8">
+      <c r="AE58" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF58" s="1">
@@ -11562,18 +11570,18 @@
       <c r="AK58" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="AL58" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1"/>
-      <c r="AO58" s="1"/>
+      <c r="AO58" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP58" s="1"/>
       <c r="AQ58" s="1" t="s">
         <v>200</v>
       </c>
       <c r="AR58" s="1"/>
-      <c r="AS58" s="9" t="s">
+      <c r="AS58" s="10" t="s">
         <v>95</v>
       </c>
       <c r="AT58" s="1">
@@ -11614,7 +11622,7 @@
       <c r="C59" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="8">
         <v>45994.71761574074</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -11644,7 +11652,7 @@
       <c r="M59" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="N59" s="7">
+      <c r="N59" s="8">
         <v>45994.74408564815</v>
       </c>
       <c r="O59" s="1" t="s">
@@ -11695,7 +11703,7 @@
       <c r="AD59" s="1">
         <v>92084.0</v>
       </c>
-      <c r="AE59" s="8">
+      <c r="AE59" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF59" s="1">
@@ -11716,26 +11724,26 @@
       <c r="AK59" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="AL59" s="4" t="s">
+      <c r="AL59" s="10"/>
+      <c r="AM59" s="10"/>
+      <c r="AN59" s="10"/>
+      <c r="AO59" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM59" s="9"/>
-      <c r="AN59" s="9"/>
-      <c r="AO59" s="9"/>
-      <c r="AP59" s="9"/>
-      <c r="AQ59" s="9" t="s">
+      <c r="AP59" s="10"/>
+      <c r="AQ59" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AR59" s="9" t="s">
+      <c r="AR59" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AS59" s="9" t="s">
+      <c r="AS59" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AT59" s="10">
+      <c r="AT59" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU59" s="10">
+      <c r="AU59" s="11">
         <v>2.0</v>
       </c>
       <c r="AV59" s="4" t="s">
@@ -11771,7 +11779,7 @@
       <c r="C60" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="8">
         <v>45994.48096064815</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -11801,7 +11809,7 @@
       <c r="M60" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="N60" s="7">
+      <c r="N60" s="8">
         <v>45994.489641203705</v>
       </c>
       <c r="O60" s="1" t="s">
@@ -11852,7 +11860,7 @@
       <c r="AD60" s="1">
         <v>90275.0</v>
       </c>
-      <c r="AE60" s="8">
+      <c r="AE60" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF60" s="1">
@@ -11873,18 +11881,18 @@
       <c r="AK60" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="AL60" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
       <c r="AN60" s="1"/>
-      <c r="AO60" s="1"/>
+      <c r="AO60" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="AP60" s="1"/>
       <c r="AQ60" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AR60" s="1"/>
-      <c r="AS60" s="9" t="s">
+      <c r="AS60" s="10" t="s">
         <v>95</v>
       </c>
       <c r="AT60" s="1">
@@ -11925,7 +11933,7 @@
       <c r="C61" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="8">
         <v>45994.58988425926</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -11955,7 +11963,7 @@
       <c r="M61" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="N61" s="7">
+      <c r="N61" s="8">
         <v>46145.97783564815</v>
       </c>
       <c r="O61" s="1" t="s">
@@ -12006,7 +12014,7 @@
       <c r="AD61" s="1">
         <v>4025748.0</v>
       </c>
-      <c r="AE61" s="8">
+      <c r="AE61" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF61" s="1">
@@ -12027,18 +12035,18 @@
       <c r="AK61" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="AL61" s="10"/>
-      <c r="AM61" s="10"/>
-      <c r="AN61" s="10"/>
-      <c r="AO61" s="10"/>
-      <c r="AP61" s="10"/>
-      <c r="AQ61" s="10"/>
-      <c r="AR61" s="10"/>
-      <c r="AS61" s="10"/>
-      <c r="AT61" s="10">
+      <c r="AL61" s="11"/>
+      <c r="AM61" s="11"/>
+      <c r="AN61" s="11"/>
+      <c r="AO61" s="11"/>
+      <c r="AP61" s="11"/>
+      <c r="AQ61" s="11"/>
+      <c r="AR61" s="11"/>
+      <c r="AS61" s="11"/>
+      <c r="AT61" s="11">
         <v>0.0</v>
       </c>
-      <c r="AU61" s="10">
+      <c r="AU61" s="11">
         <v>1.0</v>
       </c>
       <c r="AV61" s="6" t="s">
@@ -12075,7 +12083,7 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="8">
         <v>45994.60319444445</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -12105,7 +12113,7 @@
       <c r="M62" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="N62" s="7">
+      <c r="N62" s="8">
         <v>46007.26096064815</v>
       </c>
       <c r="O62" s="1" t="s">
@@ -12156,7 +12164,7 @@
       <c r="AD62" s="1">
         <v>747872.0</v>
       </c>
-      <c r="AE62" s="8">
+      <c r="AE62" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF62" s="1">
@@ -12177,18 +12185,18 @@
       <c r="AK62" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="AL62" s="10"/>
-      <c r="AM62" s="10"/>
-      <c r="AN62" s="10"/>
-      <c r="AO62" s="10"/>
-      <c r="AP62" s="10"/>
-      <c r="AQ62" s="10"/>
-      <c r="AR62" s="10"/>
-      <c r="AS62" s="10"/>
-      <c r="AT62" s="10">
+      <c r="AL62" s="11"/>
+      <c r="AM62" s="11"/>
+      <c r="AN62" s="11"/>
+      <c r="AO62" s="11"/>
+      <c r="AP62" s="11"/>
+      <c r="AQ62" s="11"/>
+      <c r="AR62" s="11"/>
+      <c r="AS62" s="11"/>
+      <c r="AT62" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU62" s="10">
+      <c r="AU62" s="11">
         <v>0.0</v>
       </c>
       <c r="AV62" s="4" t="s">
@@ -12224,7 +12232,7 @@
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="8">
         <v>45994.875451388885</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -12254,7 +12262,7 @@
       <c r="M63" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="N63" s="7">
+      <c r="N63" s="8">
         <v>45994.87703703704</v>
       </c>
       <c r="O63" s="1" t="s">
@@ -12305,7 +12313,7 @@
       <c r="AD63" s="1">
         <v>483760.0</v>
       </c>
-      <c r="AE63" s="8">
+      <c r="AE63" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF63" s="1">
@@ -12326,22 +12334,22 @@
       <c r="AK63" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="AL63" s="10"/>
-      <c r="AM63" s="10"/>
-      <c r="AN63" s="1" t="s">
+      <c r="AL63" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AO63" s="10"/>
-      <c r="AP63" s="9" t="s">
+      <c r="AM63" s="11"/>
+      <c r="AN63" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AQ63" s="10"/>
-      <c r="AR63" s="10"/>
-      <c r="AS63" s="10"/>
-      <c r="AT63" s="9">
+      <c r="AO63" s="11"/>
+      <c r="AP63" s="11"/>
+      <c r="AQ63" s="11"/>
+      <c r="AR63" s="11"/>
+      <c r="AS63" s="11"/>
+      <c r="AT63" s="10">
         <v>3.0</v>
       </c>
-      <c r="AU63" s="10">
+      <c r="AU63" s="11">
         <v>0.0</v>
       </c>
       <c r="AV63" s="4" t="s">
@@ -12377,7 +12385,7 @@
       <c r="C64" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="8">
         <v>45994.611180555556</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -12407,7 +12415,7 @@
       <c r="M64" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="N64" s="7">
+      <c r="N64" s="8">
         <v>46056.25722222222</v>
       </c>
       <c r="O64" s="1" t="s">
@@ -12458,7 +12466,7 @@
       <c r="AD64" s="1">
         <v>156287.0</v>
       </c>
-      <c r="AE64" s="8">
+      <c r="AE64" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF64" s="1">
@@ -12479,20 +12487,20 @@
       <c r="AK64" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="AL64" s="9"/>
-      <c r="AM64" s="9"/>
-      <c r="AN64" s="9"/>
-      <c r="AO64" s="9"/>
-      <c r="AP64" s="9"/>
-      <c r="AQ64" s="9"/>
-      <c r="AR64" s="9" t="s">
+      <c r="AL64" s="10"/>
+      <c r="AM64" s="10"/>
+      <c r="AN64" s="10"/>
+      <c r="AO64" s="10"/>
+      <c r="AP64" s="10"/>
+      <c r="AQ64" s="10"/>
+      <c r="AR64" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="AS64" s="9"/>
-      <c r="AT64" s="9">
+      <c r="AS64" s="10"/>
+      <c r="AT64" s="10">
         <v>1.0</v>
       </c>
-      <c r="AU64" s="9">
+      <c r="AU64" s="10">
         <v>2.0</v>
       </c>
       <c r="AV64" s="6" t="s">
@@ -12528,7 +12536,7 @@
       <c r="C65" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="8">
         <v>45995.612222222226</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -12558,7 +12566,7 @@
       <c r="M65" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="N65" s="7">
+      <c r="N65" s="8">
         <v>45995.62813657407</v>
       </c>
       <c r="O65" s="1" t="s">
@@ -12609,7 +12617,7 @@
       <c r="AD65" s="1">
         <v>141799.0</v>
       </c>
-      <c r="AE65" s="8">
+      <c r="AE65" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF65" s="1">
@@ -12630,26 +12638,26 @@
       <c r="AK65" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="AL65" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM65" s="9" t="s">
+      <c r="AL65" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM65" s="11"/>
+      <c r="AN65" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AN65" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO65" s="10"/>
-      <c r="AP65" s="9" t="s">
+      <c r="AO65" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP65" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AQ65" s="10"/>
-      <c r="AR65" s="10"/>
-      <c r="AS65" s="10"/>
-      <c r="AT65" s="10">
+      <c r="AQ65" s="11"/>
+      <c r="AR65" s="11"/>
+      <c r="AS65" s="11"/>
+      <c r="AT65" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU65" s="10">
+      <c r="AU65" s="11">
         <v>0.0</v>
       </c>
       <c r="AV65" s="6" t="s">
@@ -12685,7 +12693,7 @@
       <c r="C66" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="8">
         <v>45994.542916666665</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -12715,7 +12723,7 @@
       <c r="M66" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="N66" s="7">
+      <c r="N66" s="8">
         <v>46006.83497685185</v>
       </c>
       <c r="O66" s="1" t="s">
@@ -12766,7 +12774,7 @@
       <c r="AD66" s="1">
         <v>123650.0</v>
       </c>
-      <c r="AE66" s="8">
+      <c r="AE66" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF66" s="1">
@@ -12787,24 +12795,24 @@
       <c r="AK66" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="AL66" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM66" s="9" t="s">
+      <c r="AL66" s="10"/>
+      <c r="AM66" s="10"/>
+      <c r="AN66" s="10"/>
+      <c r="AO66" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP66" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="AN66" s="9"/>
-      <c r="AO66" s="9"/>
-      <c r="AP66" s="9"/>
-      <c r="AQ66" s="9"/>
-      <c r="AR66" s="9" t="s">
+      <c r="AQ66" s="10"/>
+      <c r="AR66" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="AS66" s="10"/>
-      <c r="AT66" s="10">
+      <c r="AS66" s="11"/>
+      <c r="AT66" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU66" s="10">
+      <c r="AU66" s="11">
         <v>1.0</v>
       </c>
       <c r="AV66" s="6" t="s">
@@ -12840,7 +12848,7 @@
       <c r="C67" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="8">
         <v>45995.64641203704</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -12870,7 +12878,7 @@
       <c r="M67" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="N67" s="7">
+      <c r="N67" s="8">
         <v>45995.677037037036</v>
       </c>
       <c r="O67" s="1" t="s">
@@ -12921,7 +12929,7 @@
       <c r="AD67" s="1">
         <v>122611.0</v>
       </c>
-      <c r="AE67" s="8">
+      <c r="AE67" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF67" s="1">
@@ -12942,18 +12950,18 @@
       <c r="AK67" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="AL67" s="10"/>
-      <c r="AM67" s="10"/>
-      <c r="AN67" s="10"/>
-      <c r="AO67" s="10"/>
-      <c r="AP67" s="10"/>
-      <c r="AQ67" s="10"/>
-      <c r="AR67" s="10"/>
-      <c r="AS67" s="10"/>
-      <c r="AT67" s="10">
+      <c r="AL67" s="11"/>
+      <c r="AM67" s="11"/>
+      <c r="AN67" s="11"/>
+      <c r="AO67" s="11"/>
+      <c r="AP67" s="11"/>
+      <c r="AQ67" s="11"/>
+      <c r="AR67" s="11"/>
+      <c r="AS67" s="11"/>
+      <c r="AT67" s="11">
         <v>1.0</v>
       </c>
-      <c r="AU67" s="10">
+      <c r="AU67" s="11">
         <v>1.0</v>
       </c>
       <c r="AV67" s="6" t="s">
@@ -12989,7 +12997,7 @@
       <c r="C68" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="8">
         <v>45994.685648148145</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -13019,7 +13027,7 @@
       <c r="M68" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="N68" s="7">
+      <c r="N68" s="8">
         <v>45994.694918981484</v>
       </c>
       <c r="O68" s="1" t="s">
@@ -13070,7 +13078,7 @@
       <c r="AD68" s="1">
         <v>109351.0</v>
       </c>
-      <c r="AE68" s="8">
+      <c r="AE68" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF68" s="1">
@@ -13091,18 +13099,18 @@
       <c r="AK68" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="AL68" s="10"/>
-      <c r="AM68" s="10"/>
-      <c r="AN68" s="10"/>
-      <c r="AO68" s="10"/>
-      <c r="AP68" s="10"/>
-      <c r="AQ68" s="10"/>
-      <c r="AR68" s="10"/>
-      <c r="AS68" s="10"/>
-      <c r="AT68" s="10">
+      <c r="AL68" s="11"/>
+      <c r="AM68" s="11"/>
+      <c r="AN68" s="11"/>
+      <c r="AO68" s="11"/>
+      <c r="AP68" s="11"/>
+      <c r="AQ68" s="11"/>
+      <c r="AR68" s="11"/>
+      <c r="AS68" s="11"/>
+      <c r="AT68" s="11">
         <v>1.0</v>
       </c>
-      <c r="AU68" s="10">
+      <c r="AU68" s="11">
         <v>1.0</v>
       </c>
       <c r="AV68" s="4" t="s">
@@ -13138,7 +13146,7 @@
       <c r="C69" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="8">
         <v>45994.45033564815</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -13168,7 +13176,7 @@
       <c r="M69" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="N69" s="7">
+      <c r="N69" s="8">
         <v>45996.08902777778</v>
       </c>
       <c r="O69" s="1" t="s">
@@ -13219,7 +13227,7 @@
       <c r="AD69" s="1">
         <v>36408.0</v>
       </c>
-      <c r="AE69" s="8">
+      <c r="AE69" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF69" s="1">
@@ -13240,22 +13248,22 @@
       <c r="AK69" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="AL69" s="9"/>
-      <c r="AM69" s="9"/>
-      <c r="AN69" s="1" t="s">
+      <c r="AL69" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AO69" s="9"/>
-      <c r="AP69" s="9" t="s">
+      <c r="AM69" s="10"/>
+      <c r="AN69" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AQ69" s="9"/>
-      <c r="AR69" s="9"/>
-      <c r="AS69" s="9"/>
-      <c r="AT69" s="9">
+      <c r="AO69" s="10"/>
+      <c r="AP69" s="10"/>
+      <c r="AQ69" s="10"/>
+      <c r="AR69" s="10"/>
+      <c r="AS69" s="10"/>
+      <c r="AT69" s="10">
         <v>2.0</v>
       </c>
-      <c r="AU69" s="10">
+      <c r="AU69" s="11">
         <v>2.0</v>
       </c>
       <c r="AV69" s="6" t="s">
@@ -13291,7 +13299,7 @@
       <c r="C70" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="8">
         <v>45994.95394675926</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -13321,7 +13329,7 @@
       <c r="M70" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="N70" s="7">
+      <c r="N70" s="8">
         <v>45995.42267361111</v>
       </c>
       <c r="O70" s="1" t="s">
@@ -13372,7 +13380,7 @@
       <c r="AD70" s="1">
         <v>81338.0</v>
       </c>
-      <c r="AE70" s="8">
+      <c r="AE70" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF70" s="1">
@@ -13393,14 +13401,14 @@
       <c r="AK70" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="AL70" s="1"/>
-      <c r="AM70" s="1"/>
-      <c r="AN70" s="1" t="s">
+      <c r="AL70" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AO70" s="1" t="s">
+      <c r="AM70" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="AN70" s="1"/>
+      <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
       <c r="AQ70" s="1"/>
       <c r="AR70" s="1"/>
@@ -13443,7 +13451,7 @@
       <c r="C71" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="8">
         <v>45994.56980324074</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -13473,7 +13481,7 @@
       <c r="M71" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="N71" s="7">
+      <c r="N71" s="8">
         <v>45994.5765625</v>
       </c>
       <c r="O71" s="1" t="s">
@@ -13524,7 +13532,7 @@
       <c r="AD71" s="1">
         <v>26185.0</v>
       </c>
-      <c r="AE71" s="8">
+      <c r="AE71" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF71" s="1">
@@ -13593,7 +13601,7 @@
       <c r="C72" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="8">
         <v>45994.57980324074</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -13623,7 +13631,7 @@
       <c r="M72" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="N72" s="7">
+      <c r="N72" s="8">
         <v>45994.58420138889</v>
       </c>
       <c r="O72" s="1" t="s">
@@ -13674,7 +13682,7 @@
       <c r="AD72" s="1">
         <v>50110.0</v>
       </c>
-      <c r="AE72" s="8">
+      <c r="AE72" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF72" s="1">
@@ -13695,15 +13703,15 @@
       <c r="AK72" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="AL72" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM72" s="1" t="s">
+      <c r="AL72" s="1"/>
+      <c r="AM72" s="1"/>
+      <c r="AN72" s="1"/>
+      <c r="AO72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP72" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AN72" s="1"/>
-      <c r="AO72" s="1"/>
-      <c r="AP72" s="1"/>
       <c r="AQ72" s="1"/>
       <c r="AR72" s="1"/>
       <c r="AS72" s="1"/>
@@ -13745,7 +13753,7 @@
       <c r="C73" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="8">
         <v>45995.22251157407</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -13775,7 +13783,7 @@
       <c r="M73" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="N73" s="7">
+      <c r="N73" s="8">
         <v>45995.22525462963</v>
       </c>
       <c r="O73" s="1" t="s">
@@ -13826,7 +13834,7 @@
       <c r="AD73" s="1">
         <v>75711.0</v>
       </c>
-      <c r="AE73" s="8">
+      <c r="AE73" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF73" s="1">
@@ -13847,10 +13855,10 @@
       <c r="AK73" s="3" t="s">
         <v>526</v>
       </c>
+      <c r="AL73" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="AN73" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP73" s="1" t="s">
         <v>110</v>
       </c>
       <c r="AQ73" s="1"/>
@@ -13894,7 +13902,7 @@
       <c r="C74" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D74" s="7">
+      <c r="D74" s="8">
         <v>45994.69449074074</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -13924,7 +13932,7 @@
       <c r="M74" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="N74" s="7">
+      <c r="N74" s="8">
         <v>45994.69703703704</v>
       </c>
       <c r="O74" s="1" t="s">
@@ -13975,7 +13983,7 @@
       <c r="AD74" s="1">
         <v>102685.0</v>
       </c>
-      <c r="AE74" s="8">
+      <c r="AE74" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF74" s="1">
@@ -14045,7 +14053,7 @@
       <c r="C75" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="8">
         <v>45994.581770833334</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -14075,7 +14083,7 @@
       <c r="M75" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="N75" s="7">
+      <c r="N75" s="8">
         <v>45994.59365740741</v>
       </c>
       <c r="O75" s="1" t="s">
@@ -14126,7 +14134,7 @@
       <c r="AD75" s="1">
         <v>40774.0</v>
       </c>
-      <c r="AE75" s="8">
+      <c r="AE75" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF75" s="1">
@@ -14195,7 +14203,7 @@
       <c r="C76" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="8">
         <v>45994.54039351852</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -14225,7 +14233,7 @@
       <c r="M76" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="N76" s="7">
+      <c r="N76" s="8">
         <v>45994.54180555556</v>
       </c>
       <c r="O76" s="1" t="s">
@@ -14276,7 +14284,7 @@
       <c r="AD76" s="1">
         <v>30815.0</v>
       </c>
-      <c r="AE76" s="8">
+      <c r="AE76" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF76" s="1">
@@ -14345,7 +14353,7 @@
       <c r="C77" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="8">
         <v>45995.382627314815</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -14375,7 +14383,7 @@
       <c r="M77" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="N77" s="7">
+      <c r="N77" s="8">
         <v>46059.015752314815</v>
       </c>
       <c r="O77" s="1" t="s">
@@ -14426,7 +14434,7 @@
       <c r="AD77" s="1">
         <v>55911.0</v>
       </c>
-      <c r="AE77" s="8">
+      <c r="AE77" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF77" s="1">
@@ -14493,7 +14501,7 @@
       <c r="C78" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="8">
         <v>45994.77371527778</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -14523,7 +14531,7 @@
       <c r="M78" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="N78" s="7">
+      <c r="N78" s="8">
         <v>45994.77532407407</v>
       </c>
       <c r="O78" s="1" t="s">
@@ -14574,7 +14582,7 @@
       <c r="AD78" s="1">
         <v>21263.0</v>
       </c>
-      <c r="AE78" s="8">
+      <c r="AE78" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF78" s="1">
@@ -14602,7 +14610,7 @@
       <c r="AP78" s="1"/>
       <c r="AQ78" s="1"/>
       <c r="AR78" s="1"/>
-      <c r="AS78" s="9" t="s">
+      <c r="AS78" s="10" t="s">
         <v>95</v>
       </c>
       <c r="AT78" s="1">
@@ -14643,7 +14651,7 @@
       <c r="C79" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="8">
         <v>45994.637557870374</v>
       </c>
       <c r="E79" s="1">
@@ -14673,7 +14681,7 @@
       <c r="M79" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="N79" s="7">
+      <c r="N79" s="8">
         <v>45994.656793981485</v>
       </c>
       <c r="O79" s="1" t="s">
@@ -14724,7 +14732,7 @@
       <c r="AD79" s="1">
         <v>62296.0</v>
       </c>
-      <c r="AE79" s="8">
+      <c r="AE79" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF79" s="1">
@@ -14745,14 +14753,14 @@
       <c r="AK79" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="AL79" s="1"/>
-      <c r="AM79" s="1"/>
-      <c r="AN79" s="1" t="s">
+      <c r="AL79" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AO79" s="1" t="s">
+      <c r="AM79" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="AN79" s="1"/>
+      <c r="AO79" s="1"/>
       <c r="AP79" s="1"/>
       <c r="AQ79" s="1"/>
       <c r="AR79" s="1"/>
@@ -14795,7 +14803,7 @@
       <c r="C80" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="8">
         <v>45994.52668981482</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -14825,7 +14833,7 @@
       <c r="M80" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="N80" s="7">
+      <c r="N80" s="8">
         <v>45994.536307870374</v>
       </c>
       <c r="O80" s="1" t="s">
@@ -14876,7 +14884,7 @@
       <c r="AD80" s="1">
         <v>22114.0</v>
       </c>
-      <c r="AE80" s="8">
+      <c r="AE80" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF80" s="1">
@@ -14943,7 +14951,7 @@
       <c r="C81" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D81" s="8">
         <v>45994.514652777776</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -14973,7 +14981,7 @@
       <c r="M81" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="N81" s="7">
+      <c r="N81" s="8">
         <v>45994.519224537034</v>
       </c>
       <c r="O81" s="1" t="s">
@@ -15024,7 +15032,7 @@
       <c r="AD81" s="1">
         <v>24083.0</v>
       </c>
-      <c r="AE81" s="8">
+      <c r="AE81" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF81" s="1">
@@ -15045,20 +15053,20 @@
       <c r="AK81" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="AL81" s="4" t="s">
+      <c r="AL81" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM81" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO81" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM81" s="1"/>
-      <c r="AN81" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO81" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="AP81" s="1"/>
       <c r="AQ81" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="AS81" s="9" t="s">
+      <c r="AS81" s="10" t="s">
         <v>95</v>
       </c>
       <c r="AT81" s="1">
@@ -15102,7 +15110,7 @@
       <c r="C82" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="8">
         <v>45994.79953703703</v>
       </c>
       <c r="E82" s="1" t="s">
@@ -15132,7 +15140,7 @@
       <c r="M82" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="N82" s="7">
+      <c r="N82" s="8">
         <v>45994.80662037037</v>
       </c>
       <c r="O82" s="1" t="s">
@@ -15183,7 +15191,7 @@
       <c r="AD82" s="1">
         <v>233352.0</v>
       </c>
-      <c r="AE82" s="8">
+      <c r="AE82" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF82" s="1">
@@ -15204,24 +15212,24 @@
       <c r="AK82" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="AL82" s="4" t="s">
+      <c r="AL82" s="10"/>
+      <c r="AM82" s="10"/>
+      <c r="AN82" s="10"/>
+      <c r="AO82" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM82" s="9"/>
-      <c r="AN82" s="9"/>
-      <c r="AO82" s="9"/>
-      <c r="AP82" s="9"/>
-      <c r="AQ82" s="11" t="s">
+      <c r="AP82" s="10"/>
+      <c r="AQ82" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="AR82" s="9" t="s">
+      <c r="AR82" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AS82" s="10"/>
-      <c r="AT82" s="10">
+      <c r="AS82" s="11"/>
+      <c r="AT82" s="11">
         <v>1.0</v>
       </c>
-      <c r="AU82" s="10">
+      <c r="AU82" s="11">
         <v>2.0</v>
       </c>
       <c r="AV82" s="6" t="s">
@@ -15259,7 +15267,7 @@
       <c r="C83" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D83" s="8">
         <v>45994.905127314814</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -15289,7 +15297,7 @@
       <c r="M83" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="N83" s="7">
+      <c r="N83" s="8">
         <v>46007.24866898148</v>
       </c>
       <c r="O83" s="1" t="s">
@@ -15340,7 +15348,7 @@
       <c r="AD83" s="1">
         <v>248158.0</v>
       </c>
-      <c r="AE83" s="8">
+      <c r="AE83" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF83" s="1">
@@ -15361,28 +15369,28 @@
       <c r="AK83" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="AL83" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM83" s="9" t="s">
+      <c r="AL83" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM83" s="11"/>
+      <c r="AN83" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AN83" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO83" s="10"/>
-      <c r="AP83" s="9" t="s">
+      <c r="AO83" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP83" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AQ83" s="11" t="s">
+      <c r="AQ83" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="AR83" s="10"/>
-      <c r="AS83" s="10"/>
-      <c r="AT83" s="10">
+      <c r="AR83" s="11"/>
+      <c r="AS83" s="11"/>
+      <c r="AT83" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU83" s="10">
+      <c r="AU83" s="11">
         <v>2.0</v>
       </c>
       <c r="AV83" s="6" t="s">
@@ -15418,7 +15426,7 @@
       <c r="C84" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D84" s="8">
         <v>45994.656747685185</v>
       </c>
       <c r="E84" s="1">
@@ -15448,7 +15456,7 @@
       <c r="M84" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="N84" s="7">
+      <c r="N84" s="8">
         <v>46012.5975</v>
       </c>
       <c r="O84" s="1" t="s">
@@ -15499,7 +15507,7 @@
       <c r="AD84" s="1">
         <v>889283.0</v>
       </c>
-      <c r="AE84" s="8">
+      <c r="AE84" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF84" s="1">
@@ -15520,28 +15528,28 @@
       <c r="AK84" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="AL84" s="4" t="s">
+      <c r="AL84" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM84" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN84" s="10"/>
+      <c r="AO84" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM84" s="9"/>
-      <c r="AN84" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO84" s="9" t="s">
+      <c r="AP84" s="10"/>
+      <c r="AQ84" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="AR84" s="10"/>
+      <c r="AS84" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AP84" s="9"/>
-      <c r="AQ84" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="AR84" s="9"/>
-      <c r="AS84" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT84" s="10">
+      <c r="AT84" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU84" s="10">
+      <c r="AU84" s="11">
         <v>1.0</v>
       </c>
       <c r="AV84" s="6" t="s">
@@ -15578,7 +15586,7 @@
       <c r="C85" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="8">
         <v>45994.89046296296</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -15608,7 +15616,7 @@
       <c r="M85" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="N85" s="7">
+      <c r="N85" s="8">
         <v>46007.255162037036</v>
       </c>
       <c r="O85" s="1" t="s">
@@ -15659,7 +15667,7 @@
       <c r="AD85" s="1">
         <v>233951.0</v>
       </c>
-      <c r="AE85" s="8">
+      <c r="AE85" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF85" s="1">
@@ -15680,28 +15688,28 @@
       <c r="AK85" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="AL85" s="4" t="s">
+      <c r="AL85" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM85" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN85" s="10"/>
+      <c r="AO85" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM85" s="9"/>
-      <c r="AN85" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO85" s="9" t="s">
+      <c r="AP85" s="10"/>
+      <c r="AQ85" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR85" s="10"/>
+      <c r="AS85" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AP85" s="9"/>
-      <c r="AQ85" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR85" s="9"/>
-      <c r="AS85" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT85" s="10">
+      <c r="AT85" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU85" s="10">
+      <c r="AU85" s="11">
         <v>2.0</v>
       </c>
       <c r="AV85" s="6" t="s">
@@ -15737,7 +15745,7 @@
       <c r="C86" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="8">
         <v>45994.573275462964</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -15767,7 +15775,7 @@
       <c r="M86" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="N86" s="7">
+      <c r="N86" s="8">
         <v>46007.25449074074</v>
       </c>
       <c r="O86" s="1" t="s">
@@ -15818,7 +15826,7 @@
       <c r="AD86" s="1">
         <v>158331.0</v>
       </c>
-      <c r="AE86" s="8">
+      <c r="AE86" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF86" s="1">
@@ -15839,24 +15847,24 @@
       <c r="AK86" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="AL86" s="4" t="s">
+      <c r="AL86" s="10"/>
+      <c r="AM86" s="10"/>
+      <c r="AN86" s="10"/>
+      <c r="AO86" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM86" s="9"/>
-      <c r="AN86" s="9"/>
-      <c r="AO86" s="9"/>
-      <c r="AP86" s="9"/>
-      <c r="AQ86" s="9" t="s">
+      <c r="AP86" s="10"/>
+      <c r="AQ86" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AR86" s="9"/>
-      <c r="AS86" s="9" t="s">
+      <c r="AR86" s="10"/>
+      <c r="AS86" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AT86" s="9">
+      <c r="AT86" s="10">
         <v>1.0</v>
       </c>
-      <c r="AU86" s="10">
+      <c r="AU86" s="11">
         <v>1.0</v>
       </c>
       <c r="AV86" s="6" t="s">
@@ -15892,7 +15900,7 @@
       <c r="C87" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D87" s="7">
+      <c r="D87" s="8">
         <v>45994.70903935185</v>
       </c>
       <c r="E87" s="1" t="s">
@@ -15922,7 +15930,7 @@
       <c r="M87" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="N87" s="7">
+      <c r="N87" s="8">
         <v>45994.71335648148</v>
       </c>
       <c r="O87" s="1" t="s">
@@ -15973,7 +15981,7 @@
       <c r="AD87" s="1">
         <v>108577.0</v>
       </c>
-      <c r="AE87" s="8">
+      <c r="AE87" s="9">
         <v>46238.0</v>
       </c>
       <c r="AF87" s="1">
@@ -15994,28 +16002,28 @@
       <c r="AK87" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="AL87" s="4" t="s">
+      <c r="AL87" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM87" s="11"/>
+      <c r="AN87" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO87" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="AM87" s="10"/>
-      <c r="AN87" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO87" s="10"/>
-      <c r="AP87" s="9" t="s">
+      <c r="AP87" s="11"/>
+      <c r="AQ87" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="AR87" s="11"/>
+      <c r="AS87" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AQ87" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="AR87" s="10"/>
-      <c r="AS87" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT87" s="10">
+      <c r="AT87" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU87" s="10">
+      <c r="AU87" s="11">
         <v>2.0</v>
       </c>
       <c r="AV87" s="6" t="s">
@@ -16053,7 +16061,7 @@
       <c r="C88" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="8">
         <v>45995.57949074074</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -16083,7 +16091,7 @@
       <c r="M88" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="N88" s="7">
+      <c r="N88" s="8">
         <v>45996.542546296296</v>
       </c>
       <c r="O88" s="1" t="s">
@@ -16134,7 +16142,7 @@
       <c r="AD88" s="1">
         <v>16414.0</v>
       </c>
-      <c r="AE88" s="8">
+      <c r="AE88" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF88" s="1">
@@ -16155,22 +16163,22 @@
       <c r="AK88" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="AL88" s="4" t="s">
+      <c r="AL88" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM88" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN88" s="1"/>
+      <c r="AO88" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="AM88" s="1"/>
-      <c r="AN88" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO88" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="AP88" s="1"/>
       <c r="AQ88" s="1" t="s">
         <v>200</v>
       </c>
       <c r="AR88" s="1"/>
-      <c r="AS88" s="9" t="s">
+      <c r="AS88" s="10" t="s">
         <v>95</v>
       </c>
       <c r="AT88" s="1">
@@ -16211,7 +16219,7 @@
       <c r="C89" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="8">
         <v>45995.87505787037</v>
       </c>
       <c r="E89" s="1" t="s">
@@ -16241,7 +16249,7 @@
       <c r="M89" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="N89" s="7">
+      <c r="N89" s="8">
         <v>46007.25649305555</v>
       </c>
       <c r="O89" s="1" t="s">
@@ -16292,7 +16300,7 @@
       <c r="AD89" s="1">
         <v>423277.0</v>
       </c>
-      <c r="AE89" s="8">
+      <c r="AE89" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF89" s="1">
@@ -16313,26 +16321,26 @@
       <c r="AK89" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="AL89" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM89" s="9" t="s">
+      <c r="AL89" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM89" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AN89" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="AO89" s="9" t="s">
+      <c r="AN89" s="11"/>
+      <c r="AO89" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP89" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AP89" s="10"/>
-      <c r="AQ89" s="10"/>
-      <c r="AR89" s="10"/>
-      <c r="AS89" s="10"/>
-      <c r="AT89" s="10">
+      <c r="AQ89" s="11"/>
+      <c r="AR89" s="11"/>
+      <c r="AS89" s="11"/>
+      <c r="AT89" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU89" s="10">
+      <c r="AU89" s="11">
         <v>0.0</v>
       </c>
       <c r="AV89" s="6" t="s">
@@ -16368,7 +16376,7 @@
       <c r="C90" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="8">
         <v>45995.50800925926</v>
       </c>
       <c r="E90" s="1" t="s">
@@ -16398,7 +16406,7 @@
       <c r="M90" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="N90" s="7">
+      <c r="N90" s="8">
         <v>46146.44793981482</v>
       </c>
       <c r="O90" s="1" t="s">
@@ -16449,7 +16457,7 @@
       <c r="AD90" s="1">
         <v>290123.0</v>
       </c>
-      <c r="AE90" s="8">
+      <c r="AE90" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF90" s="1">
@@ -16470,22 +16478,22 @@
       <c r="AK90" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="AL90" s="9"/>
-      <c r="AM90" s="9"/>
-      <c r="AN90" s="9" t="s">
+      <c r="AL90" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="AO90" s="9" t="s">
+      <c r="AM90" s="10" t="s">
         <v>95</v>
       </c>
+      <c r="AN90" s="11"/>
+      <c r="AO90" s="10"/>
       <c r="AP90" s="10"/>
-      <c r="AQ90" s="10"/>
-      <c r="AR90" s="10"/>
-      <c r="AS90" s="10"/>
-      <c r="AT90" s="10">
+      <c r="AQ90" s="11"/>
+      <c r="AR90" s="11"/>
+      <c r="AS90" s="11"/>
+      <c r="AT90" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU90" s="10">
+      <c r="AU90" s="11">
         <v>3.0</v>
       </c>
       <c r="AV90" s="6" t="s">
@@ -16521,7 +16529,7 @@
       <c r="C91" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="8">
         <v>45994.30960648148</v>
       </c>
       <c r="E91" s="1">
@@ -16551,7 +16559,7 @@
       <c r="M91" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="N91" s="7">
+      <c r="N91" s="8">
         <v>45994.522141203706</v>
       </c>
       <c r="O91" s="1" t="s">
@@ -16602,7 +16610,7 @@
       <c r="AD91" s="1">
         <v>84612.0</v>
       </c>
-      <c r="AE91" s="8">
+      <c r="AE91" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF91" s="1">
@@ -16623,22 +16631,22 @@
       <c r="AK91" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="AL91" s="9"/>
-      <c r="AM91" s="9"/>
-      <c r="AN91" s="9" t="s">
+      <c r="AL91" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="AO91" s="9" t="s">
+      <c r="AM91" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="AN91" s="11"/>
+      <c r="AO91" s="10"/>
       <c r="AP91" s="10"/>
-      <c r="AQ91" s="10"/>
-      <c r="AR91" s="10"/>
-      <c r="AS91" s="10"/>
-      <c r="AT91" s="9">
+      <c r="AQ91" s="11"/>
+      <c r="AR91" s="11"/>
+      <c r="AS91" s="11"/>
+      <c r="AT91" s="10">
         <v>2.0</v>
       </c>
-      <c r="AU91" s="10">
+      <c r="AU91" s="11">
         <v>1.0</v>
       </c>
       <c r="AV91" s="6" t="s">
@@ -16674,7 +16682,7 @@
       <c r="C92" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="8">
         <v>45995.87395833333</v>
       </c>
       <c r="E92" s="1">
@@ -16704,7 +16712,7 @@
       <c r="M92" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="N92" s="7">
+      <c r="N92" s="8">
         <v>46145.62440972222</v>
       </c>
       <c r="O92" s="1" t="s">
@@ -16755,7 +16763,7 @@
       <c r="AD92" s="1">
         <v>137508.0</v>
       </c>
-      <c r="AE92" s="8">
+      <c r="AE92" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF92" s="1">
@@ -16776,26 +16784,26 @@
       <c r="AK92" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="AL92" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM92" s="9" t="s">
+      <c r="AL92" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM92" s="11"/>
+      <c r="AN92" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AN92" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO92" s="10"/>
-      <c r="AP92" s="9" t="s">
+      <c r="AO92" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP92" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AQ92" s="10"/>
-      <c r="AR92" s="10"/>
-      <c r="AS92" s="10"/>
-      <c r="AT92" s="10">
+      <c r="AQ92" s="11"/>
+      <c r="AR92" s="11"/>
+      <c r="AS92" s="11"/>
+      <c r="AT92" s="11">
         <v>3.0</v>
       </c>
-      <c r="AU92" s="10">
+      <c r="AU92" s="11">
         <v>0.0</v>
       </c>
       <c r="AV92" s="6" t="s">
@@ -16833,7 +16841,7 @@
       <c r="C93" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="8">
         <v>45994.908680555556</v>
       </c>
       <c r="E93" s="1" t="s">
@@ -16863,7 +16871,7 @@
       <c r="M93" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="N93" s="7">
+      <c r="N93" s="8">
         <v>45994.91024305556</v>
       </c>
       <c r="O93" s="1" t="s">
@@ -16914,7 +16922,7 @@
       <c r="AD93" s="1">
         <v>46123.0</v>
       </c>
-      <c r="AE93" s="8">
+      <c r="AE93" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF93" s="1">
@@ -16935,22 +16943,22 @@
       <c r="AK93" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="AL93" s="9"/>
-      <c r="AM93" s="9"/>
-      <c r="AN93" s="9" t="s">
+      <c r="AL93" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="AO93" s="9" t="s">
+      <c r="AM93" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="AN93" s="11"/>
+      <c r="AO93" s="10"/>
       <c r="AP93" s="10"/>
-      <c r="AQ93" s="10"/>
-      <c r="AR93" s="10"/>
-      <c r="AS93" s="10"/>
-      <c r="AT93" s="10">
+      <c r="AQ93" s="11"/>
+      <c r="AR93" s="11"/>
+      <c r="AS93" s="11"/>
+      <c r="AT93" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU93" s="9">
+      <c r="AU93" s="10">
         <v>2.0</v>
       </c>
       <c r="AV93" s="6" t="s">
@@ -16987,7 +16995,7 @@
       <c r="C94" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="8">
         <v>45995.095034722224</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -17017,7 +17025,7 @@
       <c r="M94" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="N94" s="7">
+      <c r="N94" s="8">
         <v>45995.09793981481</v>
       </c>
       <c r="O94" s="1" t="s">
@@ -17068,7 +17076,7 @@
       <c r="AD94" s="1">
         <v>81840.0</v>
       </c>
-      <c r="AE94" s="8">
+      <c r="AE94" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF94" s="1">
@@ -17089,24 +17097,24 @@
       <c r="AK94" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="AL94" s="9"/>
-      <c r="AM94" s="9"/>
-      <c r="AN94" s="9" t="s">
+      <c r="AL94" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="AO94" s="9" t="s">
+      <c r="AM94" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AP94" s="9" t="s">
+      <c r="AN94" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AQ94" s="10"/>
-      <c r="AR94" s="10"/>
-      <c r="AS94" s="10"/>
-      <c r="AT94" s="10">
+      <c r="AO94" s="10"/>
+      <c r="AP94" s="10"/>
+      <c r="AQ94" s="11"/>
+      <c r="AR94" s="11"/>
+      <c r="AS94" s="11"/>
+      <c r="AT94" s="11">
         <v>2.0</v>
       </c>
-      <c r="AU94" s="10">
+      <c r="AU94" s="11">
         <v>1.0</v>
       </c>
       <c r="AV94" s="6" t="s">
@@ -17142,7 +17150,7 @@
       <c r="C95" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="8">
         <v>45994.66840277778</v>
       </c>
       <c r="E95" s="1" t="s">
@@ -17172,7 +17180,7 @@
       <c r="M95" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="N95" s="7">
+      <c r="N95" s="8">
         <v>45994.67234953704</v>
       </c>
       <c r="O95" s="1" t="s">
@@ -17223,7 +17231,7 @@
       <c r="AD95" s="1">
         <v>87212.0</v>
       </c>
-      <c r="AE95" s="8">
+      <c r="AE95" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF95" s="1">
@@ -17244,15 +17252,15 @@
       <c r="AK95" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="AL95" s="1"/>
+      <c r="AL95" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="AM95" s="1"/>
       <c r="AN95" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO95" s="1"/>
-      <c r="AP95" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="AP95" s="1"/>
       <c r="AQ95" s="1"/>
       <c r="AR95" s="1"/>
       <c r="AS95" s="1"/>
@@ -17294,7 +17302,7 @@
       <c r="C96" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="8">
         <v>45994.580092592594</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -17324,7 +17332,7 @@
       <c r="M96" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="N96" s="7">
+      <c r="N96" s="8">
         <v>45994.58924768519</v>
       </c>
       <c r="O96" s="1" t="s">
@@ -17375,7 +17383,7 @@
       <c r="AD96" s="1">
         <v>47356.0</v>
       </c>
-      <c r="AE96" s="8">
+      <c r="AE96" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF96" s="1">
@@ -17442,7 +17450,7 @@
       <c r="C97" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="8">
         <v>45994.52935185185</v>
       </c>
       <c r="E97" s="1">
@@ -17472,7 +17480,7 @@
       <c r="M97" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="N97" s="7">
+      <c r="N97" s="8">
         <v>46144.129791666666</v>
       </c>
       <c r="O97" s="1" t="s">
@@ -17523,7 +17531,7 @@
       <c r="AD97" s="1">
         <v>26506.0</v>
       </c>
-      <c r="AE97" s="8">
+      <c r="AE97" s="9">
         <v>46237.0</v>
       </c>
       <c r="AF97" s="1">
@@ -17544,16 +17552,16 @@
       <c r="AK97" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="AL97" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM97" s="1" t="s">
+      <c r="AL97" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM97" s="1"/>
+      <c r="AN97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AN97" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO97" s="1"/>
+      <c r="AO97" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="AP97" s="1" t="s">
         <v>95</v>
       </c>
@@ -17598,7 +17606,7 @@
       <c r="C98" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D98" s="7">
+      <c r="D98" s="8">
         <v>45995.01865740741</v>
       </c>
       <c r="E98" s="1" t="s">
@@ -17628,7 +17636,7 @@
       <c r="M98" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="N98" s="7">
+      <c r="N98" s="8">
         <v>45995.020833333336</v>
       </c>
       <c r="O98" s="1" t="s">
@@ -17679,7 +17687,7 @@
       <c r="AD98" s="1">
         <v>28140.0</v>
       </c>
-      <c r="AE98" s="8">
+      <c r="AE98" s="9">
         <v>46239.0</v>
       </c>
       <c r="AF98" s="1">
@@ -17700,14 +17708,14 @@
       <c r="AK98" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="AL98" s="1"/>
-      <c r="AM98" s="1"/>
-      <c r="AN98" s="1" t="s">
+      <c r="AL98" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AO98" s="1" t="s">
+      <c r="AM98" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="AN98" s="1"/>
+      <c r="AO98" s="1"/>
       <c r="AP98" s="1"/>
       <c r="AQ98" s="1"/>
       <c r="AR98" s="1"/>
